--- a/dados/dados.xlsx
+++ b/dados/dados.xlsx
@@ -167,7 +167,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gols — um gol do clube por linha: número do Jogo, Autor e Assistencia (deixe vazio se não houve assistência). Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
+          <t xml:space="preserve">Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
         </is>
       </c>
     </row>
@@ -1217,8 +1217,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -1229,10 +1230,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Minuto</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Autor</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Assistencia</t>
         </is>
@@ -1242,12 +1248,15 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Emil Novak</t>
         </is>
@@ -1257,12 +1266,15 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3">
+        <v>55</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mateo Ferreira</t>
         </is>
@@ -1272,12 +1284,15 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4">
+        <v>81</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">Kenji Sato</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">Yannick Weber</t>
         </is>
@@ -1287,12 +1302,15 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5">
+        <v>34</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">Jonas Keller</t>
         </is>
@@ -1302,12 +1320,15 @@
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6">
+        <v>67</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mateo Ferreira</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">Emil Novak</t>
         </is>
@@ -1317,7 +1338,10 @@
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7">
+        <v>78</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">Emil Novak</t>
         </is>
@@ -1327,12 +1351,15 @@
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8">
+        <v>9</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">Emil Novak</t>
         </is>
@@ -1342,12 +1369,15 @@
       <c r="A9">
         <v>4</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9">
+        <v>40</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">Jonas Keller</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">Leon Schäfer</t>
         </is>
@@ -1357,12 +1387,15 @@
       <c r="A10">
         <v>4</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10">
+        <v>88</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mateo Ferreira</t>
         </is>
@@ -1372,12 +1405,15 @@
       <c r="A11">
         <v>6</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11">
+        <v>23</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mateo Ferreira</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">Emil Novak</t>
         </is>
@@ -1387,12 +1423,15 @@
       <c r="A12">
         <v>6</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12">
+        <v>71</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">Niklas Hoffmann</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">Emil Novak</t>
         </is>
@@ -1402,12 +1441,15 @@
       <c r="A13">
         <v>7</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13">
+        <v>63</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">Paul Richter</t>
         </is>
@@ -1417,12 +1459,15 @@
       <c r="A14">
         <v>8</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14">
+        <v>18</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">Jonas Keller</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
@@ -1434,6 +1479,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t xml:space="preserve">90+3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gol contra</t>
         </is>
       </c>
@@ -1442,12 +1492,15 @@
       <c r="A16">
         <v>9</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16">
+        <v>52</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">Mateo Ferreira</t>
         </is>
@@ -1457,12 +1510,15 @@
       <c r="A17">
         <v>10</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17">
+        <v>7</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">Emil Novak</t>
         </is>
@@ -1472,12 +1528,15 @@
       <c r="A18">
         <v>10</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18">
+        <v>29</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t xml:space="preserve">Mateo Ferreira</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">Jonas Keller</t>
         </is>
@@ -1489,6 +1548,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t xml:space="preserve">45+1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
       </c>
@@ -1497,12 +1561,15 @@
       <c r="A20">
         <v>10</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20">
+        <v>84</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t xml:space="preserve">Kenji Sato</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
@@ -1512,12 +1579,15 @@
       <c r="A21">
         <v>11</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21">
+        <v>15</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t xml:space="preserve">Emil Novak</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">Felix Wagner</t>
         </is>
@@ -1527,12 +1597,15 @@
       <c r="A22">
         <v>11</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22">
+        <v>60</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t xml:space="preserve">Mateo Ferreira</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
@@ -1542,12 +1615,15 @@
       <c r="A23">
         <v>12</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23">
+        <v>38</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">Jonas Keller</t>
         </is>
@@ -1557,12 +1633,15 @@
       <c r="A24">
         <v>12</v>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24">
+        <v>74</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t xml:space="preserve">Felix Wagner</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">Emil Novak</t>
         </is>
@@ -1572,12 +1651,15 @@
       <c r="A25">
         <v>12</v>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25">
+        <v>89</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t xml:space="preserve">Mateo Ferreira</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">Lukas Brandt</t>
         </is>

--- a/dados/dados.xlsx
+++ b/dados/dados.xlsx
@@ -153,7 +153,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Episodios — um episódio por linha: número, temporada, título, data de lançamento, link do vídeo e um resumo curto.</t>
+          <t xml:space="preserve">Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade.</t>
         </is>
       </c>
     </row>
@@ -568,16 +568,6 @@
           <t xml:space="preserve">2026/27</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O recomeço: Wolfsburg na 2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15/09/2026</t>
-        </is>
-      </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Estreia da carreira: vitória fora de casa na Copa e começo de liga invicto, com Brandt já decidindo.</t>
@@ -593,16 +583,6 @@
           <t xml:space="preserve">2026/27</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Primeira derrota em Gelsenkirchen</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22/09/2026</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Goleada sobre o Karlsruhe em casa, mas o Schalke encerrou a invencibilidade na liga.</t>
@@ -618,16 +598,6 @@
           <t xml:space="preserve">2026/27</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adeus à Copa</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29/09/2026</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Vitória sobre o Paderborn, eliminação para o Werder Bremen na DFB-Pokal e empate dramático em Hannover.</t>
@@ -643,16 +613,6 @@
           <t xml:space="preserve">2026/27</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Goleada em Darmstadt</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06/10/2026</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Vitória magra contra o Nürnberg e 4 a 0 fora de casa para entrar de vez na briga pelo acesso.</t>
@@ -666,16 +626,6 @@
       <c r="B6" t="inlineStr">
         <is>
           <t xml:space="preserve">2026/27</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quatro seguidas e a briga pelo acesso</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13/10/2026</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">

--- a/dados/dados.xlsx
+++ b/dados/dados.xlsx
@@ -39,111 +39,114 @@
     <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
   </si>
   <si>
+    <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
+  </si>
+  <si>
+    <t>ABAS</t>
+  </si>
+  <si>
     <t>Episodio</t>
   </si>
   <si>
-    <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
-  </si>
-  <si>
-    <t>ABAS</t>
+    <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
+  </si>
+  <si>
+    <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
+  </si>
+  <si>
+    <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
+  </si>
+  <si>
+    <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
+  </si>
+  <si>
+    <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
+  </si>
+  <si>
+    <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
+  </si>
+  <si>
+    <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
+  </si>
+  <si>
+    <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
+  </si>
+  <si>
+    <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
+  </si>
+  <si>
+    <t>EXEMPLOS DE PREENCHIMENTO</t>
+  </si>
+  <si>
+    <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
+  </si>
+  <si>
+    <t>Chave</t>
+  </si>
+  <si>
+    <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
+  </si>
+  <si>
+    <t>Temporada</t>
   </si>
   <si>
     <t>Jogo</t>
   </si>
   <si>
-    <t>Chave</t>
-  </si>
-  <si>
-    <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
-  </si>
-  <si>
-    <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
-  </si>
-  <si>
-    <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
-  </si>
-  <si>
-    <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
-  </si>
-  <si>
-    <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
-  </si>
-  <si>
-    <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
-  </si>
-  <si>
-    <t>Temporada</t>
-  </si>
-  <si>
-    <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
-  </si>
-  <si>
     <t>Titulo</t>
   </si>
   <si>
-    <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
+    <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
   </si>
   <si>
     <t>Valor</t>
   </si>
   <si>
-    <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
+    <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
+  </si>
+  <si>
     <t>Descricao</t>
   </si>
   <si>
-    <t>EXEMPLOS DE PREENCHIMENTO</t>
+    <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
   </si>
   <si>
     <t>Link YouTube</t>
   </si>
   <si>
+    <t>Resumo</t>
+  </si>
+  <si>
+    <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
+  </si>
+  <si>
+    <t>nome_portal</t>
+  </si>
+  <si>
     <t>Competicao</t>
   </si>
   <si>
-    <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
-  </si>
-  <si>
-    <t>Resumo</t>
-  </si>
-  <si>
-    <t>nome_portal</t>
-  </si>
-  <si>
     <t>Rodada</t>
   </si>
   <si>
-    <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
-  </si>
-  <si>
-    <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
-  </si>
-  <si>
     <t>Adversario</t>
   </si>
   <si>
-    <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
-  </si>
-  <si>
     <t>Local</t>
   </si>
   <si>
-    <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
-  </si>
-  <si>
     <t>Gols Pro</t>
   </si>
   <si>
+    <t>2026/27</t>
+  </si>
+  <si>
     <t>Histórias em Campo</t>
   </si>
   <si>
-    <t>2026/27</t>
-  </si>
-  <si>
     <t>Gols Contra</t>
   </si>
   <si>
@@ -159,21 +162,21 @@
     <t>VfL Wolfsburg</t>
   </si>
   <si>
+    <t>26/27</t>
+  </si>
+  <si>
     <t>Nome do clube exatamente como aparece na aba Classificacao</t>
   </si>
   <si>
-    <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
-  </si>
-  <si>
-    <t>26/27</t>
-  </si>
-  <si>
     <t>canal</t>
   </si>
   <si>
     <t>@gabbiDOMFC</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
+  </si>
+  <si>
     <t>Nome do canal</t>
   </si>
   <si>
@@ -183,66 +186,63 @@
     <t>https://www.youtube.com/@gabbiDOMFC</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
-  </si>
-  <si>
     <t>Link do canal no YouTube</t>
   </si>
   <si>
     <t>temporada_atual</t>
   </si>
   <si>
+    <t>Temporada mostrada na página inicial</t>
+  </si>
+  <si>
+    <t>competicao_liga</t>
+  </si>
+  <si>
+    <t>2. Bundesliga</t>
+  </si>
+  <si>
+    <t>Nome da liga, igual ao usado na aba Jogos</t>
+  </si>
+  <si>
+    <t>cor_primaria</t>
+  </si>
+  <si>
+    <t>#65B32E</t>
+  </si>
+  <si>
+    <t>Cor principal do site (código hexadecimal)</t>
+  </si>
+  <si>
+    <t>cor_secundaria</t>
+  </si>
+  <si>
+    <t>#1E4D2B</t>
+  </si>
+  <si>
+    <t>Cor de apoio (fundo do topo)</t>
+  </si>
+  <si>
+    <t>escudo</t>
+  </si>
+  <si>
     <t>DFB-Pokal</t>
   </si>
   <si>
-    <t>Temporada mostrada na página inicial</t>
-  </si>
-  <si>
-    <t>competicao_liga</t>
+    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
   </si>
   <si>
     <t>1. FC Kaiserslautern</t>
   </si>
   <si>
-    <t>2. Bundesliga</t>
-  </si>
-  <si>
-    <t>Nome da liga, igual ao usado na aba Jogos</t>
-  </si>
-  <si>
-    <t>cor_primaria</t>
-  </si>
-  <si>
-    <t>#65B32E</t>
-  </si>
-  <si>
-    <t>Cor principal do site (código hexadecimal)</t>
+    <t>zona_acesso</t>
+  </si>
+  <si>
+    <t>Até esta posição: acesso direto</t>
   </si>
   <si>
     <t>Casa</t>
   </si>
   <si>
-    <t>cor_secundaria</t>
-  </si>
-  <si>
-    <t>#1E4D2B</t>
-  </si>
-  <si>
-    <t>Cor de apoio (fundo do topo)</t>
-  </si>
-  <si>
-    <t>escudo</t>
-  </si>
-  <si>
-    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
-  </si>
-  <si>
-    <t>zona_acesso</t>
-  </si>
-  <si>
-    <t>Até esta posição: acesso direto</t>
-  </si>
-  <si>
     <t>zona_playoff_acesso</t>
   </si>
   <si>
@@ -258,6 +258,9 @@
     <t>zona_rebaixamento</t>
   </si>
   <si>
+    <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
+  </si>
+  <si>
     <t>A partir desta posição: rebaixamento direto</t>
   </si>
   <si>
@@ -270,22 +273,28 @@
     <t>SIM mostra um aviso de dados de exemplo no site</t>
   </si>
   <si>
+    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
+  </si>
+  <si>
     <t>Hannover 96</t>
   </si>
   <si>
     <t>Fora</t>
   </si>
   <si>
-    <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
-  </si>
-  <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
+    <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
+  </si>
+  <si>
+    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
   </si>
   <si>
     <t>Fußball-Club Energie Cottbus</t>
@@ -294,13 +303,13 @@
     <t>FC St. Pauli</t>
   </si>
   <si>
-    <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
-  </si>
-  <si>
-    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
+    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
+  </si>
+  <si>
+    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
   </si>
   <si>
     <t>SV Darmstadt 98</t>
@@ -309,16 +318,16 @@
     <t>1. FC Nürnberg</t>
   </si>
   <si>
-    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
+    <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
   </si>
   <si>
     <t>1. Fußballclub Heidenheim 1846</t>
   </si>
   <si>
-    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
+    <t>ELE está nos salvando do PIOR! | FC 27 Modo Carreira Realista Wolfsburg| EP 05</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hc248ZsuHh8</t>
   </si>
   <si>
     <t>VfL Bochum</t>
@@ -327,22 +336,13 @@
     <t>Sport-Club Freiburg</t>
   </si>
   <si>
-    <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
-  </si>
-  <si>
-    <t>ELE está nos salvando do PIOR! | FC 27 Modo Carreira Realista Wolfsburg| EP 05</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=hc248ZsuHh8</t>
+    <t>Com os adversários cada vez mais complicados apenas um homem pode nos salvar... Descubra no episódio neste episódio!</t>
   </si>
   <si>
     <t>Verein für Leibesübungen von 1899</t>
   </si>
   <si>
     <t>Hertha BSC</t>
-  </si>
-  <si>
-    <t>Com os adversários cada vez mais complicados apenas um homem pode nos salvar... Descubra no episódio neste episódio!</t>
   </si>
   <si>
     <t xml:space="preserve">Kieler Sportvereinigung Holstein von 1900 e.V.
@@ -533,70 +533,139 @@
     <t>Grzywacz</t>
   </si>
   <si>
+    <t>Recorde</t>
+  </si>
+  <si>
+    <t>Detentor</t>
+  </si>
+  <si>
+    <t>Quando</t>
+  </si>
+  <si>
+    <t>Observacao</t>
+  </si>
+  <si>
+    <t>Confirmado</t>
+  </si>
+  <si>
+    <t>seq_vitorias</t>
+  </si>
+  <si>
     <t>MC</t>
   </si>
   <si>
+    <t>Maior sequência de vitórias</t>
+  </si>
+  <si>
     <t>Suécia</t>
   </si>
   <si>
+    <t>Bundesliga 2008/09</t>
+  </si>
+  <si>
+    <t>Sequência da campanha do título alemão</t>
+  </si>
+  <si>
     <t>Gerhardt</t>
   </si>
   <si>
+    <t>invencibilidade</t>
+  </si>
+  <si>
     <t>Kosovo</t>
   </si>
   <si>
+    <t>Maior série invicta</t>
+  </si>
+  <si>
+    <t>Preencha com o recorde real do clube</t>
+  </si>
+  <si>
     <t>Vranckx</t>
   </si>
   <si>
+    <t>maior_goleada</t>
+  </si>
+  <si>
     <t>Bélgica</t>
   </si>
   <si>
+    <t>Maior goleada (saldo de gols)</t>
+  </si>
+  <si>
+    <t>Valor = saldo de gols. Use Quando para o placar e o adversário</t>
+  </si>
+  <si>
     <t>Hensel</t>
   </si>
   <si>
+    <t>gols_temporada</t>
+  </si>
+  <si>
+    <t>Mais gols de um jogador numa temporada</t>
+  </si>
+  <si>
+    <t>Grafite</t>
+  </si>
+  <si>
     <t>Dárdai</t>
   </si>
   <si>
+    <t>Artilheiro da Bundesliga na temporada do título</t>
+  </si>
+  <si>
     <t>MEI</t>
   </si>
   <si>
     <t>Hungria</t>
   </si>
   <si>
-    <t>Recorde</t>
+    <t>assist_temporada</t>
+  </si>
+  <si>
+    <t>Mais assistências numa temporada</t>
+  </si>
+  <si>
+    <t>Kevin De Bruyne</t>
+  </si>
+  <si>
+    <t>Bundesliga 2014/15</t>
+  </si>
+  <si>
+    <t>artilheiro_historico</t>
+  </si>
+  <si>
+    <t>Maior artilheiro da história do clube</t>
   </si>
   <si>
     <t>ATA</t>
   </si>
   <si>
-    <t>Detentor</t>
-  </si>
-  <si>
-    <t>Quando</t>
-  </si>
-  <si>
-    <t>Observacao</t>
-  </si>
-  <si>
-    <t>Confirmado</t>
-  </si>
-  <si>
-    <t>seq_vitorias</t>
-  </si>
-  <si>
-    <t>Maior sequência de vitórias</t>
+    <t>Edin Džeko</t>
+  </si>
+  <si>
+    <t>2007–2011</t>
+  </si>
+  <si>
+    <t>Gols na Bundesliga</t>
+  </si>
+  <si>
+    <t>titulos</t>
   </si>
   <si>
     <t>Benedict</t>
   </si>
   <si>
+    <t>Títulos de expressão</t>
+  </si>
+  <si>
     <t>PE</t>
   </si>
   <si>
-    <t>Bundesliga 2008/09</t>
-  </si>
-  <si>
-    <t>Sequência da campanha do título alemão</t>
+    <t>2009–2015</t>
+  </si>
+  <si>
+    <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
   </si>
   <si>
     <t>Amoura</t>
@@ -608,91 +677,22 @@
     <t>Hornby</t>
   </si>
   <si>
-    <t>invencibilidade</t>
-  </si>
-  <si>
     <t>Escócia</t>
   </si>
   <si>
-    <t>Maior série invicta</t>
-  </si>
-  <si>
-    <t>Preencha com o recorde real do clube</t>
-  </si>
-  <si>
     <t>Glatzel</t>
   </si>
   <si>
-    <t>maior_goleada</t>
-  </si>
-  <si>
-    <t>Maior goleada (saldo de gols)</t>
-  </si>
-  <si>
-    <t>Valor = saldo de gols. Use Quando para o placar e o adversário</t>
-  </si>
-  <si>
     <t>Japão</t>
   </si>
   <si>
-    <t>gols_temporada</t>
-  </si>
-  <si>
-    <t>Mais gols de um jogador numa temporada</t>
-  </si>
-  <si>
     <t>Besio</t>
   </si>
   <si>
-    <t>Grafite</t>
-  </si>
-  <si>
-    <t>Artilheiro da Bundesliga na temporada do título</t>
-  </si>
-  <si>
     <t>Suíça</t>
   </si>
   <si>
-    <t>assist_temporada</t>
-  </si>
-  <si>
-    <t>Mais assistências numa temporada</t>
-  </si>
-  <si>
-    <t>Kevin De Bruyne</t>
-  </si>
-  <si>
-    <t>Bundesliga 2014/15</t>
-  </si>
-  <si>
     <t>Base</t>
-  </si>
-  <si>
-    <t>artilheiro_historico</t>
-  </si>
-  <si>
-    <t>Maior artilheiro da história do clube</t>
-  </si>
-  <si>
-    <t>Edin Džeko</t>
-  </si>
-  <si>
-    <t>2007–2011</t>
-  </si>
-  <si>
-    <t>Gols na Bundesliga</t>
-  </si>
-  <si>
-    <t>titulos</t>
-  </si>
-  <si>
-    <t>Títulos de expressão</t>
-  </si>
-  <si>
-    <t>2009–2015</t>
-  </si>
-  <si>
-    <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
   </si>
   <si>
     <t>Meta</t>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1110,52 +1110,52 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1163,32 +1163,32 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -1196,7 +1196,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -2196,13 +2196,13 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3208,35 +3208,35 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -3247,15 +3247,15 @@
         <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>53</v>
@@ -3269,59 +3269,59 @@
         <v>38</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" s="5">
         <v>2.0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -3354,18 +3354,18 @@
         <v>17.0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -4374,22 +4374,22 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -4400,16 +4400,16 @@
         <v>38</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="7">
         <v>46302.0</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -4420,16 +4420,16 @@
         <v>38</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D3" s="7">
         <v>46304.0</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
@@ -4440,16 +4440,16 @@
         <v>38</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D4" s="7">
         <v>46308.0</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
@@ -4460,16 +4460,16 @@
         <v>38</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D5" s="7">
         <v>46311.0</v>
       </c>
       <c r="E5" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -4480,16 +4480,16 @@
         <v>38</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D6" s="7">
         <v>46315.0</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5508,31 +5508,31 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2">
@@ -5543,19 +5543,19 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E2" s="6">
         <v>1.0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H2" s="6">
         <v>4.0</v>
@@ -5572,19 +5572,19 @@
         <v>1.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" s="6">
         <v>1.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H3" s="6">
         <v>4.0</v>
@@ -5601,19 +5601,19 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" s="6">
         <v>2.0</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H4" s="6">
         <v>2.0</v>
@@ -5630,19 +5630,19 @@
         <v>1.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" s="6">
         <v>3.0</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H5" s="6">
         <v>2.0</v>
@@ -5659,19 +5659,19 @@
         <v>2.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E6" s="6">
         <v>4.0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H6" s="6">
         <v>2.0</v>
@@ -5688,19 +5688,19 @@
         <v>2.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" s="6">
         <v>5.0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H7" s="6">
         <v>0.0</v>
@@ -5717,19 +5717,19 @@
         <v>2.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E8" s="6">
         <v>6.0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H8" s="6">
         <v>1.0</v>
@@ -5746,19 +5746,19 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E9" s="6">
         <v>7.0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H9" s="6">
         <v>1.0</v>
@@ -5775,19 +5775,19 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E10" s="6">
         <v>8.0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H10" s="6">
         <v>4.0</v>
@@ -5804,19 +5804,19 @@
         <v>3.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11" s="6">
         <v>9.0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H11" s="6">
         <v>1.0</v>
@@ -5833,19 +5833,19 @@
         <v>3.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E12" s="6">
         <v>2.0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H12" s="6">
         <v>0.0</v>
@@ -5862,19 +5862,19 @@
         <v>3.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E13" s="6">
         <v>10.0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H13" s="6">
         <v>5.0</v>
@@ -5891,19 +5891,19 @@
         <v>4.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E14" s="6">
         <v>11.0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H14" s="6">
         <v>3.0</v>
@@ -5920,10 +5920,10 @@
         <v>4.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E15" s="6">
         <v>12.0</v>
@@ -5932,7 +5932,7 @@
         <v>106</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6">
         <v>1.0</v>
@@ -5949,10 +5949,10 @@
         <v>4.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E16" s="6">
         <v>13.0</v>
@@ -5961,7 +5961,7 @@
         <v>107</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H16" s="6">
         <v>1.0</v>
@@ -5978,10 +5978,10 @@
         <v>5.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E17" s="6">
         <v>14.0</v>
@@ -5990,7 +5990,7 @@
         <v>108</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H17" s="6">
         <v>1.0</v>
@@ -6007,10 +6007,10 @@
         <v>5.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E18" s="6">
         <v>15.0</v>
@@ -6019,7 +6019,7 @@
         <v>109</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H18" s="6">
         <v>2.0</v>
@@ -6036,10 +6036,10 @@
         <v>5.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E19" s="6">
         <v>16.0</v>
@@ -6048,7 +6048,7 @@
         <v>110</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H19" s="6">
         <v>2.0</v>
@@ -10012,7 +10012,7 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>111</v>
@@ -11509,7 +11509,7 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>124</v>
@@ -12536,7 +12536,7 @@
     <col customWidth="1" min="3" max="3" width="9.0"/>
     <col customWidth="1" min="4" max="4" width="16.0"/>
     <col customWidth="1" min="5" max="5" width="10.75"/>
-    <col customWidth="1" min="6" max="6" width="7.75"/>
+    <col customWidth="1" min="6" max="6" width="9.38"/>
     <col customWidth="1" min="7" max="26" width="8.63"/>
   </cols>
   <sheetData>
@@ -12820,10 +12820,10 @@
         <v>119</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>141</v>
@@ -12831,10 +12831,10 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>143</v>
@@ -12848,10 +12848,10 @@
         <v>120</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>141</v>
@@ -12859,13 +12859,13 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>141</v>
@@ -12873,10 +12873,10 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>143</v>
@@ -12887,13 +12887,13 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>141</v>
@@ -12904,7 +12904,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>143</v>
@@ -12918,7 +12918,7 @@
         <v>117</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>143</v>
@@ -12932,10 +12932,10 @@
         <v>118</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>141</v>
@@ -12943,10 +12943,10 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>143</v>
@@ -12957,13 +12957,13 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>141</v>
@@ -12971,13 +12971,13 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>141</v>
@@ -12985,10 +12985,10 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>143</v>
@@ -13002,10 +13002,10 @@
         <v>115</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>141</v>
@@ -13013,13 +13013,13 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>141</v>
@@ -13030,13 +13030,13 @@
         <v>122</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>143</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F35" s="7">
         <v>46296.0</v>
@@ -14366,166 +14366,166 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C2" s="5">
         <v>10.0</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="C5" s="5">
         <v>28.0</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C6" s="5">
         <v>20.0</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="C7" s="5">
         <v>66.0</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="C8" s="5">
         <v>3.0</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -15738,7 +15738,7 @@
         <v>223</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">

--- a/dados/dados.xlsx
+++ b/dados/dados.xlsx
@@ -27,194 +27,203 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="242">
   <si>
     <t>Histórias em Campo — planilha do portal</t>
   </si>
   <si>
+    <t>Chave</t>
+  </si>
+  <si>
+    <t>Episodio</t>
+  </si>
+  <si>
+    <t>COMO USAR</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>1. Cada aba alimenta uma parte do site. Não renomeie as abas nem os títulos das colunas (linha 1).</t>
+  </si>
+  <si>
+    <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
+  </si>
+  <si>
+    <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
+  </si>
+  <si>
+    <t>Descricao</t>
+  </si>
+  <si>
+    <t>Temporada</t>
+  </si>
+  <si>
+    <t>Titulo</t>
+  </si>
+  <si>
+    <t>nome_portal</t>
+  </si>
+  <si>
     <t>Jogo</t>
   </si>
   <si>
-    <t>Chave</t>
-  </si>
-  <si>
-    <t>Episodio</t>
-  </si>
-  <si>
-    <t>COMO USAR</t>
-  </si>
-  <si>
-    <t>1. Cada aba alimenta uma parte do site. Não renomeie as abas nem os títulos das colunas (linha 1).</t>
-  </si>
-  <si>
-    <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Temporada</t>
-  </si>
-  <si>
-    <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
-  </si>
-  <si>
-    <t>Descricao</t>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>ABAS</t>
+  </si>
+  <si>
+    <t>Link YouTube</t>
+  </si>
+  <si>
+    <t>Resumo</t>
+  </si>
+  <si>
+    <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
+  </si>
+  <si>
+    <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
   </si>
   <si>
     <t>Competicao</t>
   </si>
   <si>
+    <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
+  </si>
+  <si>
     <t>Rodada</t>
   </si>
   <si>
-    <t>ABAS</t>
-  </si>
-  <si>
-    <t>nome_portal</t>
-  </si>
-  <si>
-    <t>Titulo</t>
+    <t>Histórias em Campo</t>
   </si>
   <si>
     <t>Adversario</t>
   </si>
   <si>
-    <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
   </si>
   <si>
     <t>Local</t>
   </si>
   <si>
-    <t>Data</t>
+    <t>Nome exibido no topo do site</t>
+  </si>
+  <si>
+    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
+  </si>
+  <si>
+    <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
   </si>
   <si>
     <t>Gols Pro</t>
   </si>
   <si>
+    <t>clube</t>
+  </si>
+  <si>
     <t>Gols Contra</t>
   </si>
   <si>
-    <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
-  </si>
-  <si>
-    <t>Link YouTube</t>
-  </si>
-  <si>
-    <t>Histórias em Campo</t>
-  </si>
-  <si>
-    <t>Resumo</t>
-  </si>
-  <si>
-    <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
-  </si>
-  <si>
-    <t>Nome exibido no topo do site</t>
-  </si>
-  <si>
-    <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
-  </si>
-  <si>
-    <t>clube</t>
+    <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
   </si>
   <si>
     <t>VfL Wolfsburg</t>
   </si>
   <si>
-    <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
-  </si>
-  <si>
-    <t>2026/27</t>
+    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
+  </si>
+  <si>
+    <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
+  </si>
+  <si>
+    <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
   </si>
   <si>
     <t>26/27</t>
   </si>
   <si>
-    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
-  </si>
-  <si>
-    <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
+    <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
   </si>
   <si>
     <t>canal</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
+  </si>
+  <si>
     <t>@gabbiDOMFC</t>
   </si>
   <si>
-    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
-  </si>
-  <si>
     <t>Nome do canal</t>
   </si>
   <si>
-    <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
-  </si>
-  <si>
-    <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
+    <t>EXEMPLOS DE PREENCHIMENTO</t>
   </si>
   <si>
     <t>link_canal</t>
   </si>
   <si>
+    <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/@gabbiDOMFC</t>
   </si>
   <si>
     <t>DFB-Pokal</t>
   </si>
   <si>
+    <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
+  </si>
+  <si>
     <t>Link do canal no YouTube</t>
   </si>
   <si>
-    <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
-  </si>
-  <si>
     <t>1. FC Kaiserslautern</t>
   </si>
   <si>
     <t>temporada_atual</t>
   </si>
   <si>
+    <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
+  </si>
+  <si>
     <t>Casa</t>
   </si>
   <si>
     <t>Temporada mostrada na página inicial</t>
   </si>
   <si>
-    <t>EXEMPLOS DE PREENCHIMENTO</t>
+    <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
   </si>
   <si>
     <t>competicao_liga</t>
   </si>
   <si>
+    <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
+  </si>
+  <si>
     <t>2. Bundesliga</t>
   </si>
   <si>
-    <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
-  </si>
-  <si>
     <t>Nome da liga, igual ao usado na aba Jogos</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
-  </si>
-  <si>
     <t>cor_primaria</t>
   </si>
   <si>
-    <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
-  </si>
-  <si>
     <t>#65B32E</t>
   </si>
   <si>
+    <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
+  </si>
+  <si>
     <t>Cor principal do site (código hexadecimal)</t>
   </si>
   <si>
-    <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
-  </si>
-  <si>
     <t>cor_secundaria</t>
   </si>
   <si>
@@ -224,18 +233,12 @@
     <t>Cor de apoio (fundo do topo)</t>
   </si>
   <si>
-    <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
-  </si>
-  <si>
     <t>escudo</t>
   </si>
   <si>
     <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
   </si>
   <si>
-    <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
-  </si>
-  <si>
     <t>zona_acesso</t>
   </si>
   <si>
@@ -245,18 +248,15 @@
     <t>Hannover 96</t>
   </si>
   <si>
-    <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
-  </si>
-  <si>
     <t>zona_playoff_acesso</t>
   </si>
   <si>
+    <t>Fora</t>
+  </si>
+  <si>
     <t>Posição do playoff de acesso</t>
   </si>
   <si>
-    <t>Fora</t>
-  </si>
-  <si>
     <t>zona_playoff_rebaixamento</t>
   </si>
   <si>
@@ -287,31 +287,40 @@
     <t>FC St. Pauli</t>
   </si>
   <si>
+    <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
+  </si>
+  <si>
     <t>SV Darmstadt 98</t>
   </si>
   <si>
+    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
+  </si>
+  <si>
     <t>1. FC Nürnberg</t>
   </si>
   <si>
-    <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
-  </si>
-  <si>
     <t>1. Fußballclub Heidenheim 1846</t>
   </si>
   <si>
-    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
-  </si>
-  <si>
     <t>VfL Bochum</t>
   </si>
   <si>
     <t>Sport-Club Freiburg</t>
   </si>
   <si>
+    <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
+  </si>
+  <si>
+    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
+  </si>
+  <si>
     <t>Verein für Leibesübungen von 1899</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
   </si>
   <si>
     <t>Hertha BSC</t>
@@ -325,16 +334,16 @@
 </t>
   </si>
   <si>
-    <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
+    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
+  </si>
+  <si>
+    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
   </si>
   <si>
     <t>1. FC Magdeburg</t>
   </si>
   <si>
-    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
+    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
   </si>
   <si>
     <t>SpVgg Greuther Fürth</t>
@@ -343,15 +352,6 @@
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
-  </si>
-  <si>
-    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
-  </si>
-  <si>
     <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
   </si>
   <si>
@@ -379,21 +379,21 @@
     <t>Shiogai</t>
   </si>
   <si>
+    <t>Posicao</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
     <t>Arnold</t>
   </si>
   <si>
     <t>Reese</t>
   </si>
   <si>
-    <t>Posicao</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
     <t>V</t>
   </si>
   <si>
@@ -406,12 +406,12 @@
     <t>GP</t>
   </si>
   <si>
+    <t>GC</t>
+  </si>
+  <si>
     <t>Bernhardsson</t>
   </si>
   <si>
-    <t>GC</t>
-  </si>
-  <si>
     <t>Svanberg</t>
   </si>
   <si>
@@ -433,43 +433,106 @@
     <t>Jogador</t>
   </si>
   <si>
+    <t>Numero</t>
+  </si>
+  <si>
+    <t>Nacionalidade</t>
+  </si>
+  <si>
+    <t>Origem</t>
+  </si>
+  <si>
+    <t>Chegada</t>
+  </si>
+  <si>
+    <t>Saida</t>
+  </si>
+  <si>
+    <t>Grabara</t>
+  </si>
+  <si>
+    <t>GOL</t>
+  </si>
+  <si>
+    <t>Polônia</t>
+  </si>
+  <si>
+    <t>Elenco inicial</t>
+  </si>
+  <si>
+    <t>Wellenreuther</t>
+  </si>
+  <si>
+    <t>Alemanha</t>
+  </si>
+  <si>
+    <t>Pervan</t>
+  </si>
+  <si>
+    <t>Áustria</t>
+  </si>
+  <si>
+    <t>Zieliński</t>
+  </si>
+  <si>
+    <t>Vavro</t>
+  </si>
+  <si>
+    <t>ZAG</t>
+  </si>
+  <si>
+    <t>Eslováquia</t>
+  </si>
+  <si>
+    <t>Wahl</t>
+  </si>
+  <si>
+    <t>Jenz</t>
+  </si>
+  <si>
+    <t>Adjetey</t>
+  </si>
+  <si>
+    <t>Gana</t>
+  </si>
+  <si>
     <t>Recorde</t>
   </si>
   <si>
-    <t>Numero</t>
+    <t>Cleiton</t>
+  </si>
+  <si>
+    <t>Brasil</t>
   </si>
   <si>
     <t>Detentor</t>
   </si>
   <si>
-    <t>Nacionalidade</t>
-  </si>
-  <si>
     <t>Quando</t>
   </si>
   <si>
+    <t>Angély</t>
+  </si>
+  <si>
     <t>Observacao</t>
   </si>
   <si>
-    <t>Origem</t>
-  </si>
-  <si>
     <t>Confirmado</t>
   </si>
   <si>
-    <t>Chegada</t>
-  </si>
-  <si>
-    <t>Saida</t>
+    <t>França</t>
   </si>
   <si>
     <t>seq_vitorias</t>
   </si>
   <si>
+    <t>Kumbedi</t>
+  </si>
+  <si>
     <t>Maior sequência de vitórias</t>
   </si>
   <si>
-    <t>Grabara</t>
+    <t>LD</t>
   </si>
   <si>
     <t>Bundesliga 2008/09</t>
@@ -478,25 +541,10 @@
     <t>Sequência da campanha do título alemão</t>
   </si>
   <si>
-    <t>GOL</t>
-  </si>
-  <si>
-    <t>invencibilidade</t>
-  </si>
-  <si>
-    <t>Polônia</t>
-  </si>
-  <si>
-    <t>Maior série invicta</t>
-  </si>
-  <si>
-    <t>Elenco inicial</t>
-  </si>
-  <si>
-    <t>Preencha com o recorde real do clube</t>
-  </si>
-  <si>
-    <t>Wellenreuther</t>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>SIM</t>
   </si>
   <si>
     <t>maior_goleada</t>
@@ -505,13 +553,19 @@
     <t>Maior goleada (saldo de gols)</t>
   </si>
   <si>
-    <t>Valor = saldo de gols. Use Quando para o placar e o adversário</t>
-  </si>
-  <si>
-    <t>Alemanha</t>
-  </si>
-  <si>
-    <t>Pervan</t>
+    <t>9 × 0 SV Hemelingen</t>
+  </si>
+  <si>
+    <t>Mæhle</t>
+  </si>
+  <si>
+    <t>16/08/2025 · DFB-Pokal, 1ª fase</t>
+  </si>
+  <si>
+    <t>Recorde do clube na competição, confirmado pelo Wolfsburg</t>
+  </si>
+  <si>
+    <t>Dinamarca</t>
   </si>
   <si>
     <t>gols_temporada</t>
@@ -520,21 +574,24 @@
     <t>Mais gols de um jogador numa temporada</t>
   </si>
   <si>
-    <t>Áustria</t>
+    <t>Zehnter</t>
   </si>
   <si>
     <t>Grafite</t>
   </si>
   <si>
+    <t>LE</t>
+  </si>
+  <si>
     <t>Artilheiro da Bundesliga na temporada do título</t>
   </si>
   <si>
-    <t>Zieliński</t>
-  </si>
-  <si>
     <t>assist_temporada</t>
   </si>
   <si>
+    <t>Rogério</t>
+  </si>
+  <si>
     <t>Mais assistências numa temporada</t>
   </si>
   <si>
@@ -544,10 +601,7 @@
     <t>Bundesliga 2014/15</t>
   </si>
   <si>
-    <t>Vavro</t>
-  </si>
-  <si>
-    <t>ZAG</t>
+    <t>Recorde da Bundesliga na época</t>
   </si>
   <si>
     <t>artilheiro_historico</t>
@@ -556,7 +610,7 @@
     <t>Maior artilheiro da história do clube</t>
   </si>
   <si>
-    <t>Eslováquia</t>
+    <t>VOL</t>
   </si>
   <si>
     <t>Edin Džeko</t>
@@ -568,9 +622,6 @@
     <t>Gols na Bundesliga</t>
   </si>
   <si>
-    <t>Wahl</t>
-  </si>
-  <si>
     <t>titulos</t>
   </si>
   <si>
@@ -580,57 +631,9 @@
     <t>2009–2015</t>
   </si>
   <si>
-    <t>Jenz</t>
-  </si>
-  <si>
     <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
   </si>
   <si>
-    <t>Adjetey</t>
-  </si>
-  <si>
-    <t>Gana</t>
-  </si>
-  <si>
-    <t>Cleiton</t>
-  </si>
-  <si>
-    <t>Brasil</t>
-  </si>
-  <si>
-    <t>Angély</t>
-  </si>
-  <si>
-    <t>França</t>
-  </si>
-  <si>
-    <t>Kumbedi</t>
-  </si>
-  <si>
-    <t>LD</t>
-  </si>
-  <si>
-    <t>Fischer</t>
-  </si>
-  <si>
-    <t>Mæhle</t>
-  </si>
-  <si>
-    <t>Dinamarca</t>
-  </si>
-  <si>
-    <t>Zehnter</t>
-  </si>
-  <si>
-    <t>LE</t>
-  </si>
-  <si>
-    <t>Rogério</t>
-  </si>
-  <si>
-    <t>VOL</t>
-  </si>
-  <si>
     <t>Grzywacz</t>
   </si>
   <si>
@@ -733,10 +736,10 @@
     <t>https://upload.wikimedia.org/wikipedia/de/thumb/4/45/Logo_Eintracht_Braunschweig.svg/250px-Logo_Eintracht_Braunschweig.svg.png</t>
   </si>
   <si>
+    <t>Eintracht-Stadion</t>
+  </si>
+  <si>
     <t>Tipo</t>
-  </si>
-  <si>
-    <t>Eintracht-Stadion</t>
   </si>
   <si>
     <t>Idade</t>
@@ -781,14 +784,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
-      <color rgb="FF2E7D32"/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11.0"/>
+      <color rgb="FF2E7D32"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -845,10 +848,10 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -865,7 +868,7 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -1141,8 +1144,8 @@
       <c r="A2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
+      <c r="A3" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1157,15 +1160,15 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>13</v>
+      <c r="A8" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -1175,42 +1178,42 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1218,32 +1221,32 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -1251,7 +1254,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -2250,14 +2253,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>139</v>
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3262,21 +3265,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>235</v>
@@ -3302,66 +3305,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="12" t="s">
         <v>133</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B2" s="6">
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F2" s="6">
         <v>34.0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I2" s="6">
         <v>0.0</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -3383,22 +3386,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>10</v>
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>27</v>
@@ -3406,98 +3409,98 @@
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" s="5">
         <v>2.0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
@@ -3508,7 +3511,7 @@
         <v>3.0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -4549,23 +4552,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>25</v>
+      <c r="F1" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2">
@@ -4573,19 +4576,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D2" s="7">
         <v>46302.0</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -4593,19 +4596,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D3" s="7">
         <v>46304.0</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4">
@@ -4613,19 +4616,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D4" s="7">
         <v>46308.0</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="5">
@@ -4633,16 +4636,16 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D5" s="7">
         <v>46311.0</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>107</v>
@@ -4653,7 +4656,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>108</v>
@@ -5683,32 +5686,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -5719,19 +5722,19 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E2" s="6">
         <v>1.0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H2" s="6">
         <v>4.0</v>
@@ -5748,19 +5751,19 @@
         <v>1.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E3" s="6">
         <v>1.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H3" s="6">
         <v>4.0</v>
@@ -5777,19 +5780,19 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E4" s="6">
         <v>2.0</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H4" s="6">
         <v>2.0</v>
@@ -5806,10 +5809,10 @@
         <v>1.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E5" s="6">
         <v>3.0</v>
@@ -5818,7 +5821,7 @@
         <v>80</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H5" s="6">
         <v>2.0</v>
@@ -5835,10 +5838,10 @@
         <v>2.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E6" s="6">
         <v>4.0</v>
@@ -5847,7 +5850,7 @@
         <v>84</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H6" s="6">
         <v>2.0</v>
@@ -5864,10 +5867,10 @@
         <v>2.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E7" s="6">
         <v>5.0</v>
@@ -5876,7 +5879,7 @@
         <v>85</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H7" s="6">
         <v>0.0</v>
@@ -5893,19 +5896,19 @@
         <v>2.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E8" s="6">
         <v>6.0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H8" s="6">
         <v>1.0</v>
@@ -5922,19 +5925,19 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E9" s="6">
         <v>7.0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H9" s="6">
         <v>1.0</v>
@@ -5951,19 +5954,19 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E10" s="6">
         <v>8.0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H10" s="6">
         <v>4.0</v>
@@ -5980,10 +5983,10 @@
         <v>3.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E11" s="6">
         <v>9.0</v>
@@ -5992,7 +5995,7 @@
         <v>92</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H11" s="6">
         <v>1.0</v>
@@ -6009,10 +6012,10 @@
         <v>3.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E12" s="6">
         <v>2.0</v>
@@ -6021,7 +6024,7 @@
         <v>93</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H12" s="6">
         <v>0.0</v>
@@ -6038,19 +6041,19 @@
         <v>3.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E13" s="6">
         <v>10.0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H13" s="6">
         <v>5.0</v>
@@ -6067,19 +6070,19 @@
         <v>4.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E14" s="6">
         <v>11.0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H14" s="6">
         <v>3.0</v>
@@ -6096,19 +6099,19 @@
         <v>4.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E15" s="6">
         <v>12.0</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H15" s="6">
         <v>1.0</v>
@@ -6125,19 +6128,19 @@
         <v>4.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E16" s="6">
         <v>13.0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H16" s="6">
         <v>1.0</v>
@@ -6154,19 +6157,19 @@
         <v>5.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E17" s="6">
         <v>14.0</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H17" s="6">
         <v>1.0</v>
@@ -6183,19 +6186,19 @@
         <v>5.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E18" s="6">
         <v>15.0</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H18" s="6">
         <v>2.0</v>
@@ -6212,19 +6215,19 @@
         <v>5.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E19" s="6">
         <v>16.0</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H19" s="6">
         <v>2.0</v>
@@ -10187,16 +10190,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>113</v>
       </c>
     </row>
@@ -10236,10 +10239,10 @@
         <v>50.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5">
@@ -10250,7 +10253,7 @@
         <v>57.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>114</v>
@@ -10267,7 +10270,7 @@
         <v>115</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -10281,7 +10284,7 @@
         <v>115</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8">
@@ -10292,7 +10295,7 @@
         <v>59.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
@@ -10306,7 +10309,7 @@
         <v>115</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -10320,7 +10323,7 @@
         <v>115</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -10342,7 +10345,7 @@
         <v>45.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>127</v>
@@ -10356,7 +10359,7 @@
         <v>82.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>127</v>
@@ -10387,7 +10390,7 @@
         <v>115</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -10401,7 +10404,7 @@
         <v>115</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
@@ -10440,10 +10443,10 @@
         <v>35.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -10524,7 +10527,7 @@
         <v>39.0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>114</v>
@@ -10569,7 +10572,7 @@
         <v>115</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -10583,7 +10586,7 @@
         <v>114</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -10611,7 +10614,7 @@
         <v>114</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -10622,7 +10625,7 @@
         <v>82.0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>127</v>
@@ -10636,7 +10639,7 @@
         <v>47.0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>114</v>
@@ -11684,32 +11687,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>126</v>
+      <c r="I1" s="3" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="2">
@@ -11720,7 +11723,7 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D2" s="6">
         <v>16.0</v>
@@ -11836,7 +11839,7 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D6" s="6">
         <v>16.0</v>
@@ -12895,246 +12898,246 @@
         <v>133</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C1" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="G1" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
@@ -13142,27 +13145,27 @@
         <v>132</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
@@ -13170,27 +13173,27 @@
         <v>127</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -13198,55 +13201,55 @@
         <v>129</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -13254,97 +13257,97 @@
         <v>114</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -13352,27 +13355,27 @@
         <v>115</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -13380,13 +13383,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F35" s="6">
         <v>3.0</v>
@@ -14715,168 +14718,169 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>141</v>
+      <c r="A1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="A2" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="6">
         <v>10.0</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>82</v>
+      <c r="D2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>82</v>
+      <c r="A3" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="6">
+        <v>9.0</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>82</v>
+      <c r="A4" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="6">
+        <v>28.0</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C5" s="5">
-        <v>28.0</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>82</v>
+      <c r="A5" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="5">
-        <v>20.0</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="5" t="s">
-        <v>82</v>
+      <c r="A6" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="6">
+        <v>66.0</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="5">
-        <v>66.0</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>82</v>
+      <c r="A7" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C7" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C8" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>82</v>
-      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9">
       <c r="G9" s="5"/>
@@ -16081,33 +16085,33 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>139</v>
+      <c r="B1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C3" s="2"/>
     </row>

--- a/dados/dados.xlsx
+++ b/dados/dados.xlsx
@@ -27,258 +27,267 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="268">
+  <si>
+    <t>Chave</t>
+  </si>
+  <si>
+    <t>Episodio</t>
+  </si>
   <si>
     <t>Histórias em Campo — planilha do portal</t>
   </si>
   <si>
-    <t>Chave</t>
-  </si>
-  <si>
-    <t>Episodio</t>
+    <t>Jogo</t>
   </si>
   <si>
     <t>COMO USAR</t>
   </si>
   <si>
+    <t>1. Cada aba alimenta uma parte do site. Não renomeie as abas nem os títulos das colunas (linha 1).</t>
+  </si>
+  <si>
+    <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
+  </si>
+  <si>
     <t>Valor</t>
   </si>
   <si>
-    <t>1. Cada aba alimenta uma parte do site. Não renomeie as abas nem os títulos das colunas (linha 1).</t>
-  </si>
-  <si>
-    <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
-  </si>
-  <si>
     <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
   </si>
   <si>
     <t>Descricao</t>
   </si>
   <si>
+    <t>ABAS</t>
+  </si>
+  <si>
+    <t>nome_portal</t>
+  </si>
+  <si>
+    <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
+  </si>
+  <si>
+    <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
+  </si>
+  <si>
+    <t>Histórias em Campo</t>
+  </si>
+  <si>
     <t>Temporada</t>
   </si>
   <si>
+    <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
+  </si>
+  <si>
+    <t>Nome exibido no topo do site</t>
+  </si>
+  <si>
     <t>Titulo</t>
   </si>
   <si>
-    <t>nome_portal</t>
-  </si>
-  <si>
-    <t>Jogo</t>
+    <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
+  </si>
+  <si>
+    <t>clube</t>
   </si>
   <si>
     <t>Data</t>
   </si>
   <si>
-    <t>ABAS</t>
+    <t>VfL Wolfsburg</t>
+  </si>
+  <si>
+    <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
+  </si>
+  <si>
+    <t>Competicao</t>
+  </si>
+  <si>
+    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
   </si>
   <si>
     <t>Link YouTube</t>
   </si>
   <si>
+    <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
+  </si>
+  <si>
+    <t>canal</t>
+  </si>
+  <si>
+    <t>@gabbiDOMFC</t>
+  </si>
+  <si>
     <t>Resumo</t>
   </si>
   <si>
-    <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
-  </si>
-  <si>
-    <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
-  </si>
-  <si>
-    <t>Competicao</t>
-  </si>
-  <si>
-    <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
-  </si>
-  <si>
     <t>Rodada</t>
   </si>
   <si>
-    <t>Histórias em Campo</t>
+    <t>Nome do canal</t>
+  </si>
+  <si>
+    <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
+  </si>
+  <si>
+    <t>link_canal</t>
   </si>
   <si>
     <t>Adversario</t>
   </si>
   <si>
+    <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@gabbiDOMFC</t>
+  </si>
+  <si>
+    <t>Link do canal no YouTube</t>
+  </si>
+  <si>
+    <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>temporada_atual</t>
+  </si>
+  <si>
     <t>2026/27</t>
   </si>
   <si>
-    <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>Nome exibido no topo do site</t>
+    <t>EXEMPLOS DE PREENCHIMENTO</t>
+  </si>
+  <si>
+    <t>Gols Pro</t>
+  </si>
+  <si>
+    <t>Temporada mostrada na página inicial</t>
+  </si>
+  <si>
+    <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
+  </si>
+  <si>
+    <t>Gols Contra</t>
+  </si>
+  <si>
+    <t>competicao_liga</t>
+  </si>
+  <si>
+    <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
+  </si>
+  <si>
+    <t>2. Bundesliga</t>
   </si>
   <si>
     <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
   </si>
   <si>
-    <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
-  </si>
-  <si>
-    <t>Gols Pro</t>
-  </si>
-  <si>
-    <t>clube</t>
-  </si>
-  <si>
-    <t>Gols Contra</t>
-  </si>
-  <si>
-    <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
-  </si>
-  <si>
-    <t>VfL Wolfsburg</t>
-  </si>
-  <si>
-    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
-  </si>
-  <si>
-    <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
-  </si>
-  <si>
-    <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
+    <t>Nome da liga, igual ao usado na aba Jogos</t>
+  </si>
+  <si>
+    <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
+  </si>
+  <si>
+    <t>cor_primaria</t>
+  </si>
+  <si>
+    <t>#65B32E</t>
+  </si>
+  <si>
+    <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
+  </si>
+  <si>
+    <t>Cor principal do site (código hexadecimal)</t>
+  </si>
+  <si>
+    <t>cor_secundaria</t>
+  </si>
+  <si>
+    <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
+  </si>
+  <si>
+    <t>#1E4D2B</t>
+  </si>
+  <si>
+    <t>Cor de apoio (fundo do topo)</t>
+  </si>
+  <si>
+    <t>escudo</t>
+  </si>
+  <si>
+    <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
+  </si>
+  <si>
+    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
+  </si>
+  <si>
+    <t>zona_acesso</t>
+  </si>
+  <si>
+    <t>Até esta posição: acesso direto</t>
+  </si>
+  <si>
+    <t>zona_playoff_acesso</t>
+  </si>
+  <si>
+    <t>Posição do playoff de acesso</t>
+  </si>
+  <si>
+    <t>zona_playoff_rebaixamento</t>
   </si>
   <si>
     <t>26/27</t>
   </si>
   <si>
-    <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
-  </si>
-  <si>
-    <t>canal</t>
+    <t>Posição do playoff de rebaixamento</t>
+  </si>
+  <si>
+    <t>zona_rebaixamento</t>
+  </si>
+  <si>
+    <t>A partir desta posição: rebaixamento direto</t>
+  </si>
+  <si>
+    <t>dados_exemplo</t>
+  </si>
+  <si>
+    <t>NAO</t>
+  </si>
+  <si>
+    <t>SIM mostra um aviso de dados de exemplo no site</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
   </si>
   <si>
-    <t>@gabbiDOMFC</t>
-  </si>
-  <si>
-    <t>Nome do canal</t>
-  </si>
-  <si>
-    <t>EXEMPLOS DE PREENCHIMENTO</t>
-  </si>
-  <si>
-    <t>link_canal</t>
-  </si>
-  <si>
-    <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/@gabbiDOMFC</t>
-  </si>
-  <si>
     <t>DFB-Pokal</t>
   </si>
   <si>
-    <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
-  </si>
-  <si>
-    <t>Link do canal no YouTube</t>
-  </si>
-  <si>
     <t>1. FC Kaiserslautern</t>
   </si>
   <si>
-    <t>temporada_atual</t>
-  </si>
-  <si>
-    <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
-  </si>
-  <si>
     <t>Casa</t>
   </si>
   <si>
-    <t>Temporada mostrada na página inicial</t>
-  </si>
-  <si>
-    <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
-  </si>
-  <si>
-    <t>competicao_liga</t>
-  </si>
-  <si>
-    <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
-  </si>
-  <si>
-    <t>2. Bundesliga</t>
-  </si>
-  <si>
-    <t>Nome da liga, igual ao usado na aba Jogos</t>
-  </si>
-  <si>
-    <t>cor_primaria</t>
-  </si>
-  <si>
-    <t>#65B32E</t>
-  </si>
-  <si>
-    <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
-  </si>
-  <si>
-    <t>Cor principal do site (código hexadecimal)</t>
-  </si>
-  <si>
-    <t>cor_secundaria</t>
-  </si>
-  <si>
-    <t>#1E4D2B</t>
-  </si>
-  <si>
-    <t>Cor de apoio (fundo do topo)</t>
-  </si>
-  <si>
-    <t>escudo</t>
-  </si>
-  <si>
-    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
-  </si>
-  <si>
-    <t>zona_acesso</t>
-  </si>
-  <si>
-    <t>Até esta posição: acesso direto</t>
-  </si>
-  <si>
     <t>Hannover 96</t>
   </si>
   <si>
-    <t>zona_playoff_acesso</t>
-  </si>
-  <si>
     <t>Fora</t>
   </si>
   <si>
-    <t>Posição do playoff de acesso</t>
-  </si>
-  <si>
-    <t>zona_playoff_rebaixamento</t>
-  </si>
-  <si>
-    <t>Posição do playoff de rebaixamento</t>
-  </si>
-  <si>
-    <t>zona_rebaixamento</t>
-  </si>
-  <si>
-    <t>A partir desta posição: rebaixamento direto</t>
-  </si>
-  <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
-    <t>dados_exemplo</t>
-  </si>
-  <si>
-    <t>NAO</t>
-  </si>
-  <si>
-    <t>SIM mostra um aviso de dados de exemplo no site</t>
+    <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
+  </si>
+  <si>
+    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
   </si>
   <si>
     <t>Fußball-Club Energie Cottbus</t>
@@ -287,21 +296,21 @@
     <t>FC St. Pauli</t>
   </si>
   <si>
-    <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
-  </si>
-  <si>
     <t>SV Darmstadt 98</t>
   </si>
   <si>
-    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
+    <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
   </si>
   <si>
     <t>1. FC Nürnberg</t>
   </si>
   <si>
+    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
+  </si>
+  <si>
     <t>1. Fußballclub Heidenheim 1846</t>
   </si>
   <si>
@@ -311,16 +320,16 @@
     <t>Sport-Club Freiburg</t>
   </si>
   <si>
-    <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
-  </si>
-  <si>
-    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
+    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
+  </si>
+  <si>
+    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
   </si>
   <si>
     <t>Verein für Leibesübungen von 1899</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
   </si>
   <si>
     <t>Hertha BSC</t>
@@ -334,33 +343,24 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
-  </si>
-  <si>
-    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
+    <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
+  </si>
+  <si>
+    <t>ELE está nos salvando do PIOR! | FC 27 Modo Carreira Realista Wolfsburg| EP 05</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hc248ZsuHh8</t>
   </si>
   <si>
     <t>1. FC Magdeburg</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
-  </si>
-  <si>
     <t>SpVgg Greuther Fürth</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
-  </si>
-  <si>
-    <t>ELE está nos salvando do PIOR! | FC 27 Modo Carreira Realista Wolfsburg| EP 05</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=hc248ZsuHh8</t>
-  </si>
-  <si>
     <t>Com os adversários cada vez mais complicados apenas um homem pode nos salvar... Descubra no episódio neste episódio!</t>
   </si>
   <si>
@@ -376,30 +376,30 @@
     <t>Damar</t>
   </si>
   <si>
+    <t>Posicao</t>
+  </si>
+  <si>
     <t>Shiogai</t>
   </si>
   <si>
-    <t>Posicao</t>
-  </si>
-  <si>
     <t>Time</t>
   </si>
   <si>
     <t>J</t>
   </si>
   <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
     <t>Arnold</t>
   </si>
   <si>
     <t>Reese</t>
   </si>
   <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -430,6 +430,33 @@
     <t>Vinicius Souza</t>
   </si>
   <si>
+    <t>Recorde</t>
+  </si>
+  <si>
+    <t>Detentor</t>
+  </si>
+  <si>
+    <t>Quando</t>
+  </si>
+  <si>
+    <t>Observacao</t>
+  </si>
+  <si>
+    <t>Confirmado</t>
+  </si>
+  <si>
+    <t>seq_vitorias</t>
+  </si>
+  <si>
+    <t>Maior sequência de vitórias</t>
+  </si>
+  <si>
+    <t>Bundesliga 2008/09</t>
+  </si>
+  <si>
+    <t>Sequência da campanha do título alemão</t>
+  </si>
+  <si>
     <t>Jogador</t>
   </si>
   <si>
@@ -439,18 +466,48 @@
     <t>Nacionalidade</t>
   </si>
   <si>
+    <t>SIM</t>
+  </si>
+  <si>
     <t>Origem</t>
   </si>
   <si>
+    <t>maior_goleada</t>
+  </si>
+  <si>
+    <t>Maior goleada (saldo de gols)</t>
+  </si>
+  <si>
     <t>Chegada</t>
   </si>
   <si>
+    <t>9 × 0 SV Hemelingen</t>
+  </si>
+  <si>
+    <t>16/08/2025 · DFB-Pokal, 1ª fase</t>
+  </si>
+  <si>
     <t>Saida</t>
   </si>
   <si>
+    <t>Recorde do clube na competição, confirmado pelo Wolfsburg</t>
+  </si>
+  <si>
     <t>Grabara</t>
   </si>
   <si>
+    <t>gols_temporada</t>
+  </si>
+  <si>
+    <t>Mais gols de um jogador numa temporada</t>
+  </si>
+  <si>
+    <t>Grafite</t>
+  </si>
+  <si>
+    <t>Artilheiro da Bundesliga na temporada do título</t>
+  </si>
+  <si>
     <t>GOL</t>
   </si>
   <si>
@@ -463,30 +520,72 @@
     <t>Wellenreuther</t>
   </si>
   <si>
+    <t>assist_temporada</t>
+  </si>
+  <si>
+    <t>Mais assistências numa temporada</t>
+  </si>
+  <si>
     <t>Alemanha</t>
   </si>
   <si>
+    <t>Kevin De Bruyne</t>
+  </si>
+  <si>
+    <t>Bundesliga 2014/15</t>
+  </si>
+  <si>
+    <t>Recorde da Bundesliga na época</t>
+  </si>
+  <si>
     <t>Pervan</t>
   </si>
   <si>
     <t>Áustria</t>
   </si>
   <si>
+    <t>artilheiro_historico</t>
+  </si>
+  <si>
+    <t>Maior artilheiro da história do clube</t>
+  </si>
+  <si>
     <t>Zieliński</t>
   </si>
   <si>
+    <t>Edin Džeko</t>
+  </si>
+  <si>
+    <t>2007–2011</t>
+  </si>
+  <si>
+    <t>Gols na Bundesliga</t>
+  </si>
+  <si>
     <t>Vavro</t>
   </si>
   <si>
+    <t>titulos</t>
+  </si>
+  <si>
     <t>ZAG</t>
   </si>
   <si>
     <t>Eslováquia</t>
   </si>
   <si>
+    <t>Títulos de expressão</t>
+  </si>
+  <si>
     <t>Wahl</t>
   </si>
   <si>
+    <t>2009–2015</t>
+  </si>
+  <si>
+    <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
+  </si>
+  <si>
     <t>Jenz</t>
   </si>
   <si>
@@ -496,144 +595,45 @@
     <t>Gana</t>
   </si>
   <si>
-    <t>Recorde</t>
-  </si>
-  <si>
     <t>Cleiton</t>
   </si>
   <si>
     <t>Brasil</t>
   </si>
   <si>
-    <t>Detentor</t>
-  </si>
-  <si>
-    <t>Quando</t>
-  </si>
-  <si>
     <t>Angély</t>
   </si>
   <si>
-    <t>Observacao</t>
-  </si>
-  <si>
-    <t>Confirmado</t>
-  </si>
-  <si>
     <t>França</t>
   </si>
   <si>
-    <t>seq_vitorias</t>
-  </si>
-  <si>
     <t>Kumbedi</t>
   </si>
   <si>
-    <t>Maior sequência de vitórias</t>
-  </si>
-  <si>
     <t>LD</t>
   </si>
   <si>
-    <t>Bundesliga 2008/09</t>
-  </si>
-  <si>
-    <t>Sequência da campanha do título alemão</t>
-  </si>
-  <si>
     <t>Fischer</t>
   </si>
   <si>
-    <t>SIM</t>
-  </si>
-  <si>
-    <t>maior_goleada</t>
-  </si>
-  <si>
-    <t>Maior goleada (saldo de gols)</t>
-  </si>
-  <si>
-    <t>9 × 0 SV Hemelingen</t>
-  </si>
-  <si>
     <t>Mæhle</t>
   </si>
   <si>
-    <t>16/08/2025 · DFB-Pokal, 1ª fase</t>
-  </si>
-  <si>
-    <t>Recorde do clube na competição, confirmado pelo Wolfsburg</t>
-  </si>
-  <si>
     <t>Dinamarca</t>
   </si>
   <si>
-    <t>gols_temporada</t>
-  </si>
-  <si>
-    <t>Mais gols de um jogador numa temporada</t>
-  </si>
-  <si>
     <t>Zehnter</t>
   </si>
   <si>
-    <t>Grafite</t>
-  </si>
-  <si>
     <t>LE</t>
   </si>
   <si>
-    <t>Artilheiro da Bundesliga na temporada do título</t>
-  </si>
-  <si>
-    <t>assist_temporada</t>
-  </si>
-  <si>
     <t>Rogério</t>
   </si>
   <si>
-    <t>Mais assistências numa temporada</t>
-  </si>
-  <si>
-    <t>Kevin De Bruyne</t>
-  </si>
-  <si>
-    <t>Bundesliga 2014/15</t>
-  </si>
-  <si>
-    <t>Recorde da Bundesliga na época</t>
-  </si>
-  <si>
-    <t>artilheiro_historico</t>
-  </si>
-  <si>
-    <t>Maior artilheiro da história do clube</t>
-  </si>
-  <si>
     <t>VOL</t>
   </si>
   <si>
-    <t>Edin Džeko</t>
-  </si>
-  <si>
-    <t>2007–2011</t>
-  </si>
-  <si>
-    <t>Gols na Bundesliga</t>
-  </si>
-  <si>
-    <t>titulos</t>
-  </si>
-  <si>
-    <t>Títulos de expressão</t>
-  </si>
-  <si>
-    <t>2009–2015</t>
-  </si>
-  <si>
-    <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
-  </si>
-  <si>
     <t>Grzywacz</t>
   </si>
   <si>
@@ -649,79 +649,160 @@
     <t>Kosovo</t>
   </si>
   <si>
+    <t>Meta</t>
+  </si>
+  <si>
     <t>Vranckx</t>
   </si>
   <si>
     <t>Bélgica</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Hensel</t>
   </si>
   <si>
+    <t>Imagem</t>
+  </si>
+  <si>
     <t>Dárdai</t>
   </si>
   <si>
+    <t>Atual</t>
+  </si>
+  <si>
     <t>MEI</t>
   </si>
   <si>
+    <t>Alvo</t>
+  </si>
+  <si>
     <t>Hungria</t>
   </si>
   <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Subir como campeão</t>
+  </si>
+  <si>
     <t>ATA</t>
   </si>
   <si>
+    <t>Em andamento</t>
+  </si>
+  <si>
+    <t>Conquistar o título da 2. Bundesliga e o acesso direto</t>
+  </si>
+  <si>
     <t>Benedict</t>
   </si>
   <si>
+    <t>subir-campeao.svg</t>
+  </si>
+  <si>
     <t>PE</t>
   </si>
   <si>
+    <t>Chegar às oitavas da DFB-Pokal</t>
+  </si>
+  <si>
     <t>Amoura</t>
   </si>
   <si>
+    <t>Falhou</t>
+  </si>
+  <si>
+    <t>Eliminados pelo Freiburg na 2ª fase</t>
+  </si>
+  <si>
+    <t>oitavas-pokal.svg</t>
+  </si>
+  <si>
     <t>Argélia</t>
   </si>
   <si>
     <t>Hornby</t>
   </si>
   <si>
+    <t>Encontrar um novo D'Alessandro</t>
+  </si>
+  <si>
     <t>Escócia</t>
   </si>
   <si>
     <t>Glatzel</t>
   </si>
   <si>
+    <t>MEI argentino, canhoto, de 15 a 23 anos</t>
+  </si>
+  <si>
+    <t>novo-dalessandro.svg</t>
+  </si>
+  <si>
+    <t>Scouting Sul-Americano</t>
+  </si>
+  <si>
     <t>Japão</t>
   </si>
   <si>
+    <t>Ter no elenco no mínimo 5 jogadores sul-americanos</t>
+  </si>
+  <si>
+    <t>scouting-sulamericano.svg</t>
+  </si>
+  <si>
     <t>Besio</t>
   </si>
   <si>
     <t>Suíça</t>
   </si>
   <si>
+    <t>sulamericanos</t>
+  </si>
+  <si>
+    <t>Academia do Wolfsburg</t>
+  </si>
+  <si>
+    <t>Categorias de base na Alemanha e na Argentina</t>
+  </si>
+  <si>
+    <t>academia.svg</t>
+  </si>
+  <si>
     <t>Base</t>
   </si>
   <si>
-    <t>Meta</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Conquistar o acesso à Bundesliga na 1ª temporada</t>
-  </si>
-  <si>
-    <t>Em andamento</t>
-  </si>
-  <si>
-    <t>Terminar entre os 2 primeiros ou vencer o playoff</t>
-  </si>
-  <si>
-    <t>Ir longe na DFB-Pokal</t>
-  </si>
-  <si>
-    <t>Falhou</t>
+    <t>Regras de contratação por janela</t>
+  </si>
+  <si>
+    <t>Vendeu € 10 mi: pode gastar até € 5 mi; Vendeu € 20 mi: até € 8 mi; Vendeu € 30 mi: até € 12 mi; Vendeu € 40 mi: até € 15 mi; Vendeu € 50 mi: até € 20 mi; Vendeu € 60 mi: até € 25 mi; Acima de € 60 mi: até 50% do valor das vendas</t>
+  </si>
+  <si>
+    <t>regras-transferencias.svg</t>
+  </si>
+  <si>
+    <t>Regra</t>
+  </si>
+  <si>
+    <t>Estilo de jogo</t>
+  </si>
+  <si>
+    <t>Inspirado no Internacional campeão da Sul-Americana 2008, no tradicional 4-3-1-2</t>
+  </si>
+  <si>
+    <t>estilo-de-jogo.svg</t>
+  </si>
+  <si>
+    <t>Regras de saída de jogadores</t>
+  </si>
+  <si>
+    <t>Só podemos recusar propostas de compra se estivermos em 1º ou 2º lugar na Bundesliga</t>
+  </si>
+  <si>
+    <t>regras-saida.svg</t>
   </si>
   <si>
     <t>Clube</t>
@@ -737,9 +818,6 @@
   </si>
   <si>
     <t>Eintracht-Stadion</t>
-  </si>
-  <si>
-    <t>Tipo</t>
   </si>
   <si>
     <t>Idade</t>
@@ -784,14 +862,14 @@
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11.0"/>
+      <color rgb="FF2E7D32"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
-      <color rgb="FF2E7D32"/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -848,10 +926,10 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -868,7 +946,7 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -1137,15 +1215,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
+      <c r="A3" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1160,55 +1238,55 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>14</v>
+      <c r="A8" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1221,7 +1299,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20">
@@ -1246,7 +1324,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -2253,14 +2331,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>161</v>
+      <c r="A1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3265,24 +3343,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3305,66 +3383,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B2" s="6">
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>239</v>
+        <v>265</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F2" s="6">
         <v>34.0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="I2" s="6">
         <v>0.0</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -3386,14 +3464,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>8</v>
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2">
@@ -3401,150 +3479,150 @@
         <v>11</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B11" s="5">
         <v>2.0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B12" s="5">
         <v>3.0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B13" s="5">
         <v>16.0</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B14" s="5">
         <v>17.0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -4552,23 +4630,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>16</v>
+      <c r="C1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2">
@@ -4576,19 +4654,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="D2" s="7">
         <v>46302.0</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -4596,19 +4674,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D3" s="7">
         <v>46304.0</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
@@ -4616,19 +4694,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D4" s="7">
         <v>46308.0</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>97</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="5">
@@ -4636,19 +4714,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D5" s="7">
         <v>46311.0</v>
       </c>
       <c r="E5" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="6">
@@ -4656,16 +4734,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D6" s="7">
         <v>46315.0</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>110</v>
@@ -5686,32 +5764,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>32</v>
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -5722,19 +5800,19 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E2" s="6">
         <v>1.0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H2" s="6">
         <v>4.0</v>
@@ -5751,19 +5829,19 @@
         <v>1.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E3" s="6">
         <v>1.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H3" s="6">
         <v>4.0</v>
@@ -5780,19 +5858,19 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E4" s="6">
         <v>2.0</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H4" s="6">
         <v>2.0</v>
@@ -5809,19 +5887,19 @@
         <v>1.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E5" s="6">
         <v>3.0</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H5" s="6">
         <v>2.0</v>
@@ -5838,19 +5916,19 @@
         <v>2.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E6" s="6">
         <v>4.0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H6" s="6">
         <v>2.0</v>
@@ -5867,19 +5945,19 @@
         <v>2.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E7" s="6">
         <v>5.0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H7" s="6">
         <v>0.0</v>
@@ -5896,19 +5974,19 @@
         <v>2.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E8" s="6">
         <v>6.0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H8" s="6">
         <v>1.0</v>
@@ -5925,19 +6003,19 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E9" s="6">
         <v>7.0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H9" s="6">
         <v>1.0</v>
@@ -5954,19 +6032,19 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E10" s="6">
         <v>8.0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H10" s="6">
         <v>4.0</v>
@@ -5983,19 +6061,19 @@
         <v>3.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E11" s="6">
         <v>9.0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H11" s="6">
         <v>1.0</v>
@@ -6012,19 +6090,19 @@
         <v>3.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="E12" s="6">
         <v>2.0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H12" s="6">
         <v>0.0</v>
@@ -6041,19 +6119,19 @@
         <v>3.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E13" s="6">
         <v>10.0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H13" s="6">
         <v>5.0</v>
@@ -6070,19 +6148,19 @@
         <v>4.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E14" s="6">
         <v>11.0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H14" s="6">
         <v>3.0</v>
@@ -6099,19 +6177,19 @@
         <v>4.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E15" s="6">
         <v>12.0</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H15" s="6">
         <v>1.0</v>
@@ -6128,19 +6206,19 @@
         <v>4.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E16" s="6">
         <v>13.0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H16" s="6">
         <v>1.0</v>
@@ -6157,19 +6235,19 @@
         <v>5.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E17" s="6">
         <v>14.0</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H17" s="6">
         <v>1.0</v>
@@ -6186,19 +6264,19 @@
         <v>5.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E18" s="6">
         <v>15.0</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H18" s="6">
         <v>2.0</v>
@@ -6215,19 +6293,19 @@
         <v>5.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E19" s="6">
         <v>16.0</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="H19" s="6">
         <v>2.0</v>
@@ -10190,16 +10268,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>113</v>
       </c>
     </row>
@@ -10214,7 +10292,7 @@
         <v>114</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3">
@@ -10225,7 +10303,7 @@
         <v>38.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>114</v>
@@ -10239,10 +10317,10 @@
         <v>50.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
@@ -10253,7 +10331,7 @@
         <v>57.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>114</v>
@@ -10267,10 +10345,10 @@
         <v>17.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -10281,10 +10359,10 @@
         <v>42.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8">
@@ -10295,7 +10373,7 @@
         <v>59.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9">
@@ -10306,7 +10384,7 @@
         <v>86.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>126</v>
@@ -10320,10 +10398,10 @@
         <v>28.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -10345,7 +10423,7 @@
         <v>45.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>127</v>
@@ -10359,7 +10437,7 @@
         <v>82.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>127</v>
@@ -10373,7 +10451,7 @@
         <v>8.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>127</v>
@@ -10387,10 +10465,10 @@
         <v>80.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -10401,7 +10479,7 @@
         <v>75.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>126</v>
@@ -10415,7 +10493,7 @@
         <v>73.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>114</v>
@@ -10429,7 +10507,7 @@
         <v>28.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>114</v>
@@ -10443,10 +10521,10 @@
         <v>35.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20">
@@ -10457,7 +10535,7 @@
         <v>40.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>114</v>
@@ -10471,7 +10549,7 @@
         <v>88.0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>114</v>
@@ -10485,7 +10563,7 @@
         <v>28.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>114</v>
@@ -10499,7 +10577,7 @@
         <v>27.0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>114</v>
@@ -10513,7 +10591,7 @@
         <v>37.0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>114</v>
@@ -10527,7 +10605,7 @@
         <v>39.0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>114</v>
@@ -10541,7 +10619,7 @@
         <v>56.0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>129</v>
@@ -10569,7 +10647,7 @@
         <v>4.0</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>126</v>
@@ -10653,7 +10731,7 @@
         <v>3.0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>132</v>
@@ -10667,7 +10745,7 @@
         <v>63.0</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>127</v>
@@ -10681,7 +10759,7 @@
         <v>74.0</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>131</v>
@@ -10695,7 +10773,7 @@
         <v>82.0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>131</v>
@@ -11687,31 +11765,31 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>125</v>
       </c>
     </row>
@@ -11723,7 +11801,7 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D2" s="6">
         <v>16.0</v>
@@ -11752,7 +11830,7 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D3" s="6">
         <v>16.0</v>
@@ -11810,7 +11888,7 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D5" s="6">
         <v>16.0</v>
@@ -11839,7 +11917,7 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" s="6">
         <v>16.0</v>
@@ -11868,7 +11946,7 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D7" s="6">
         <v>16.0</v>
@@ -12895,249 +12973,249 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18">
@@ -13145,13 +13223,13 @@
         <v>132</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19">
@@ -13159,13 +13237,13 @@
         <v>201</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20">
@@ -13179,7 +13257,7 @@
         <v>203</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -13190,10 +13268,10 @@
         <v>202</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -13207,49 +13285,49 @@
         <v>205</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>202</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>202</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -13257,27 +13335,27 @@
         <v>114</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -13285,97 +13363,97 @@
         <v>126</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>203</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>212</v>
-      </c>
       <c r="D32" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -13386,10 +13464,10 @@
         <v>202</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="F35" s="6">
         <v>3.0</v>
@@ -14719,163 +14797,163 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="C2" s="6">
         <v>10.0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="C3" s="6">
         <v>9.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C4" s="6">
         <v>28.0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="C5" s="6">
         <v>20.0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C6" s="6">
         <v>66.0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C7" s="6">
         <v>3.0</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8">
@@ -16085,53 +16163,169 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="9" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C3" s="2"/>
+      <c r="H3" s="6" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="4">
-      <c r="B4" s="5"/>
+      <c r="A4" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="5"/>
+      <c r="A5" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" s="5"/>
+      <c r="A6" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>248</v>
+      </c>
       <c r="B7" s="5"/>
+      <c r="C7" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="8">
+      <c r="A8" s="6" t="s">
+        <v>252</v>
+      </c>
       <c r="B8" s="5"/>
+      <c r="C8" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="9">
+      <c r="A9" s="6" t="s">
+        <v>255</v>
+      </c>
       <c r="B9" s="5"/>
+      <c r="C9" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="5"/>

--- a/dados/dados.xlsx
+++ b/dados/dados.xlsx
@@ -35,243 +35,243 @@
     <t>Episodio</t>
   </si>
   <si>
+    <t>Jogo</t>
+  </si>
+  <si>
     <t>Histórias em Campo — planilha do portal</t>
   </si>
   <si>
-    <t>Jogo</t>
-  </si>
-  <si>
     <t>COMO USAR</t>
   </si>
   <si>
+    <t>Valor</t>
+  </si>
+  <si>
     <t>1. Cada aba alimenta uma parte do site. Não renomeie as abas nem os títulos das colunas (linha 1).</t>
   </si>
   <si>
+    <t>Descricao</t>
+  </si>
+  <si>
     <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
   </si>
   <si>
-    <t>Valor</t>
+    <t>nome_portal</t>
   </si>
   <si>
     <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
   </si>
   <si>
-    <t>Descricao</t>
-  </si>
-  <si>
     <t>ABAS</t>
   </si>
   <si>
-    <t>nome_portal</t>
+    <t>Temporada</t>
+  </si>
+  <si>
+    <t>Histórias em Campo</t>
   </si>
   <si>
     <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
   </si>
   <si>
+    <t>Titulo</t>
+  </si>
+  <si>
+    <t>Nome exibido no topo do site</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
     <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
   </si>
   <si>
-    <t>Histórias em Campo</t>
-  </si>
-  <si>
-    <t>Temporada</t>
+    <t>clube</t>
+  </si>
+  <si>
+    <t>Link YouTube</t>
+  </si>
+  <si>
+    <t>Competicao</t>
+  </si>
+  <si>
+    <t>VfL Wolfsburg</t>
+  </si>
+  <si>
+    <t>Resumo</t>
+  </si>
+  <si>
+    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
+  </si>
+  <si>
+    <t>Rodada</t>
   </si>
   <si>
     <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
   </si>
   <si>
-    <t>Nome exibido no topo do site</t>
-  </si>
-  <si>
-    <t>Titulo</t>
+    <t>canal</t>
+  </si>
+  <si>
+    <t>Adversario</t>
+  </si>
+  <si>
+    <t>@gabbiDOMFC</t>
+  </si>
+  <si>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>Nome do canal</t>
   </si>
   <si>
     <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
   </si>
   <si>
-    <t>clube</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>VfL Wolfsburg</t>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>link_canal</t>
+  </si>
+  <si>
+    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@gabbiDOMFC</t>
+  </si>
+  <si>
+    <t>Gols Pro</t>
+  </si>
+  <si>
+    <t>Link do canal no YouTube</t>
   </si>
   <si>
     <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
   </si>
   <si>
-    <t>Competicao</t>
-  </si>
-  <si>
-    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
-  </si>
-  <si>
-    <t>Link YouTube</t>
+    <t>Gols Contra</t>
+  </si>
+  <si>
+    <t>temporada_atual</t>
+  </si>
+  <si>
+    <t>Temporada mostrada na página inicial</t>
+  </si>
+  <si>
+    <t>competicao_liga</t>
   </si>
   <si>
     <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
   </si>
   <si>
-    <t>canal</t>
-  </si>
-  <si>
-    <t>@gabbiDOMFC</t>
-  </si>
-  <si>
-    <t>Resumo</t>
-  </si>
-  <si>
-    <t>Rodada</t>
-  </si>
-  <si>
-    <t>Nome do canal</t>
+    <t>2. Bundesliga</t>
+  </si>
+  <si>
+    <t>26/27</t>
+  </si>
+  <si>
+    <t>Nome da liga, igual ao usado na aba Jogos</t>
+  </si>
+  <si>
+    <t>cor_primaria</t>
   </si>
   <si>
     <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
   </si>
   <si>
-    <t>link_canal</t>
-  </si>
-  <si>
-    <t>Adversario</t>
+    <t>#65B32E</t>
+  </si>
+  <si>
+    <t>Cor principal do site (código hexadecimal)</t>
   </si>
   <si>
     <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
   </si>
   <si>
-    <t>https://www.youtube.com/@gabbiDOMFC</t>
-  </si>
-  <si>
-    <t>Link do canal no YouTube</t>
+    <t>cor_secundaria</t>
+  </si>
+  <si>
+    <t>#1E4D2B</t>
+  </si>
+  <si>
+    <t>Cor de apoio (fundo do topo)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
   </si>
   <si>
     <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
   </si>
   <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>temporada_atual</t>
-  </si>
-  <si>
-    <t>2026/27</t>
+    <t>escudo</t>
+  </si>
+  <si>
+    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
   </si>
   <si>
     <t>EXEMPLOS DE PREENCHIMENTO</t>
   </si>
   <si>
-    <t>Gols Pro</t>
-  </si>
-  <si>
-    <t>Temporada mostrada na página inicial</t>
+    <t>zona_acesso</t>
+  </si>
+  <si>
+    <t>Até esta posição: acesso direto</t>
   </si>
   <si>
     <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
   </si>
   <si>
-    <t>Gols Contra</t>
-  </si>
-  <si>
-    <t>competicao_liga</t>
+    <t>zona_playoff_acesso</t>
   </si>
   <si>
     <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
   </si>
   <si>
-    <t>2. Bundesliga</t>
-  </si>
-  <si>
-    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
-  </si>
-  <si>
-    <t>Nome da liga, igual ao usado na aba Jogos</t>
+    <t>Posição do playoff de acesso</t>
   </si>
   <si>
     <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
   </si>
   <si>
-    <t>cor_primaria</t>
-  </si>
-  <si>
-    <t>#65B32E</t>
+    <t>zona_playoff_rebaixamento</t>
   </si>
   <si>
     <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
   </si>
   <si>
-    <t>Cor principal do site (código hexadecimal)</t>
-  </si>
-  <si>
-    <t>cor_secundaria</t>
+    <t>Posição do playoff de rebaixamento</t>
+  </si>
+  <si>
+    <t>DFB-Pokal</t>
   </si>
   <si>
     <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
   </si>
   <si>
-    <t>#1E4D2B</t>
-  </si>
-  <si>
-    <t>Cor de apoio (fundo do topo)</t>
-  </si>
-  <si>
-    <t>escudo</t>
+    <t>zona_rebaixamento</t>
+  </si>
+  <si>
+    <t>1. FC Kaiserslautern</t>
+  </si>
+  <si>
+    <t>A partir desta posição: rebaixamento direto</t>
   </si>
   <si>
     <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
   </si>
   <si>
-    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
-  </si>
-  <si>
-    <t>zona_acesso</t>
-  </si>
-  <si>
-    <t>Até esta posição: acesso direto</t>
-  </si>
-  <si>
-    <t>zona_playoff_acesso</t>
-  </si>
-  <si>
-    <t>Posição do playoff de acesso</t>
-  </si>
-  <si>
-    <t>zona_playoff_rebaixamento</t>
-  </si>
-  <si>
-    <t>26/27</t>
-  </si>
-  <si>
-    <t>Posição do playoff de rebaixamento</t>
-  </si>
-  <si>
-    <t>zona_rebaixamento</t>
-  </si>
-  <si>
-    <t>A partir desta posição: rebaixamento direto</t>
-  </si>
-  <si>
     <t>dados_exemplo</t>
   </si>
   <si>
+    <t>Casa</t>
+  </si>
+  <si>
     <t>NAO</t>
   </si>
   <si>
     <t>SIM mostra um aviso de dados de exemplo no site</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
-  </si>
-  <si>
-    <t>DFB-Pokal</t>
-  </si>
-  <si>
-    <t>1. FC Kaiserslautern</t>
-  </si>
-  <si>
-    <t>Casa</t>
-  </si>
-  <si>
     <t>Hannover 96</t>
   </si>
   <si>
@@ -281,68 +281,77 @@
     <t>Karlsruher SC</t>
   </si>
   <si>
+    <t>Fußball-Club Energie Cottbus</t>
+  </si>
+  <si>
+    <t>FC St. Pauli</t>
+  </si>
+  <si>
+    <t>SV Darmstadt 98</t>
+  </si>
+  <si>
     <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
   </si>
   <si>
+    <t>1. FC Nürnberg</t>
+  </si>
+  <si>
     <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
   </si>
   <si>
-    <t>Fußball-Club Energie Cottbus</t>
-  </si>
-  <si>
-    <t>FC St. Pauli</t>
-  </si>
-  <si>
-    <t>SV Darmstadt 98</t>
+    <t>1. Fußballclub Heidenheim 1846</t>
+  </si>
+  <si>
+    <t>VfL Bochum</t>
+  </si>
+  <si>
+    <t>Sport-Club Freiburg</t>
+  </si>
+  <si>
+    <t>Verein für Leibesübungen von 1899</t>
+  </si>
+  <si>
+    <t>Hertha BSC</t>
   </si>
   <si>
     <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
-  </si>
-  <si>
-    <t>1. FC Nürnberg</t>
-  </si>
-  <si>
-    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
-  </si>
-  <si>
-    <t>1. Fußballclub Heidenheim 1846</t>
-  </si>
-  <si>
-    <t>VfL Bochum</t>
-  </si>
-  <si>
-    <t>Sport-Club Freiburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
-  </si>
-  <si>
-    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
-  </si>
-  <si>
-    <t>Verein für Leibesübungen von 1899</t>
-  </si>
-  <si>
-    <t>Hertha BSC</t>
   </si>
   <si>
     <t xml:space="preserve">Kieler Sportvereinigung Holstein von 1900 e.V.
 </t>
   </si>
   <si>
+    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
+  </si>
+  <si>
     <t xml:space="preserve">Eintracht Braunschweig
 </t>
   </si>
   <si>
+    <t>1. FC Magdeburg</t>
+  </si>
+  <si>
+    <t>SpVgg Greuther Fürth</t>
+  </si>
+  <si>
+    <t>Arminia Bielefeld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
+  </si>
+  <si>
+    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
+  </si>
+  <si>
     <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
   </si>
   <si>
@@ -352,15 +361,6 @@
     <t>https://www.youtube.com/watch?v=hc248ZsuHh8</t>
   </si>
   <si>
-    <t>1. FC Magdeburg</t>
-  </si>
-  <si>
-    <t>SpVgg Greuther Fürth</t>
-  </si>
-  <si>
-    <t>Arminia Bielefeld</t>
-  </si>
-  <si>
     <t>Com os adversários cada vez mais complicados apenas um homem pode nos salvar... Descubra no episódio neste episódio!</t>
   </si>
   <si>
@@ -376,12 +376,24 @@
     <t>Damar</t>
   </si>
   <si>
+    <t>Shiogai</t>
+  </si>
+  <si>
+    <t>Arnold</t>
+  </si>
+  <si>
+    <t>Reese</t>
+  </si>
+  <si>
+    <t>Bernhardsson</t>
+  </si>
+  <si>
+    <t>Svanberg</t>
+  </si>
+  <si>
     <t>Posicao</t>
   </si>
   <si>
-    <t>Shiogai</t>
-  </si>
-  <si>
     <t>Time</t>
   </si>
   <si>
@@ -394,12 +406,6 @@
     <t>E</t>
   </si>
   <si>
-    <t>Arnold</t>
-  </si>
-  <si>
-    <t>Reese</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -409,18 +415,12 @@
     <t>GC</t>
   </si>
   <si>
-    <t>Bernhardsson</t>
-  </si>
-  <si>
-    <t>Svanberg</t>
+    <t>Rexhbeçaj</t>
   </si>
   <si>
     <t>Eintracht Braunschweig</t>
   </si>
   <si>
-    <t>Rexhbeçaj</t>
-  </si>
-  <si>
     <t>Dardai</t>
   </si>
   <si>
@@ -430,6 +430,180 @@
     <t>Vinicius Souza</t>
   </si>
   <si>
+    <t>Jogador</t>
+  </si>
+  <si>
+    <t>Numero</t>
+  </si>
+  <si>
+    <t>Nacionalidade</t>
+  </si>
+  <si>
+    <t>Origem</t>
+  </si>
+  <si>
+    <t>Chegada</t>
+  </si>
+  <si>
+    <t>Saida</t>
+  </si>
+  <si>
+    <t>Grabara</t>
+  </si>
+  <si>
+    <t>GOL</t>
+  </si>
+  <si>
+    <t>Polônia</t>
+  </si>
+  <si>
+    <t>Elenco inicial</t>
+  </si>
+  <si>
+    <t>Wellenreuther</t>
+  </si>
+  <si>
+    <t>Alemanha</t>
+  </si>
+  <si>
+    <t>Pervan</t>
+  </si>
+  <si>
+    <t>Áustria</t>
+  </si>
+  <si>
+    <t>Zieliński</t>
+  </si>
+  <si>
+    <t>Vavro</t>
+  </si>
+  <si>
+    <t>ZAG</t>
+  </si>
+  <si>
+    <t>Eslováquia</t>
+  </si>
+  <si>
+    <t>Wahl</t>
+  </si>
+  <si>
+    <t>Jenz</t>
+  </si>
+  <si>
+    <t>Adjetey</t>
+  </si>
+  <si>
+    <t>Gana</t>
+  </si>
+  <si>
+    <t>Cleiton</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>Angély</t>
+  </si>
+  <si>
+    <t>França</t>
+  </si>
+  <si>
+    <t>Kumbedi</t>
+  </si>
+  <si>
+    <t>LD</t>
+  </si>
+  <si>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>Mæhle</t>
+  </si>
+  <si>
+    <t>Dinamarca</t>
+  </si>
+  <si>
+    <t>Zehnter</t>
+  </si>
+  <si>
+    <t>LE</t>
+  </si>
+  <si>
+    <t>Rogério</t>
+  </si>
+  <si>
+    <t>VOL</t>
+  </si>
+  <si>
+    <t>Grzywacz</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Suécia</t>
+  </si>
+  <si>
+    <t>Gerhardt</t>
+  </si>
+  <si>
+    <t>Kosovo</t>
+  </si>
+  <si>
+    <t>Vranckx</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
+  </si>
+  <si>
+    <t>Hensel</t>
+  </si>
+  <si>
+    <t>Dárdai</t>
+  </si>
+  <si>
+    <t>MEI</t>
+  </si>
+  <si>
+    <t>Hungria</t>
+  </si>
+  <si>
+    <t>ATA</t>
+  </si>
+  <si>
+    <t>Benedict</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>Amoura</t>
+  </si>
+  <si>
+    <t>Argélia</t>
+  </si>
+  <si>
+    <t>Hornby</t>
+  </si>
+  <si>
+    <t>Escócia</t>
+  </si>
+  <si>
+    <t>Glatzel</t>
+  </si>
+  <si>
+    <t>Japão</t>
+  </si>
+  <si>
+    <t>Besio</t>
+  </si>
+  <si>
+    <t>Suíça</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
     <t>Recorde</t>
   </si>
   <si>
@@ -457,45 +631,24 @@
     <t>Sequência da campanha do título alemão</t>
   </si>
   <si>
-    <t>Jogador</t>
-  </si>
-  <si>
-    <t>Numero</t>
-  </si>
-  <si>
-    <t>Nacionalidade</t>
-  </si>
-  <si>
     <t>SIM</t>
   </si>
   <si>
-    <t>Origem</t>
-  </si>
-  <si>
     <t>maior_goleada</t>
   </si>
   <si>
     <t>Maior goleada (saldo de gols)</t>
   </si>
   <si>
-    <t>Chegada</t>
-  </si>
-  <si>
     <t>9 × 0 SV Hemelingen</t>
   </si>
   <si>
     <t>16/08/2025 · DFB-Pokal, 1ª fase</t>
   </si>
   <si>
-    <t>Saida</t>
-  </si>
-  <si>
     <t>Recorde do clube na competição, confirmado pelo Wolfsburg</t>
   </si>
   <si>
-    <t>Grabara</t>
-  </si>
-  <si>
     <t>gols_temporada</t>
   </si>
   <si>
@@ -508,27 +661,12 @@
     <t>Artilheiro da Bundesliga na temporada do título</t>
   </si>
   <si>
-    <t>GOL</t>
-  </si>
-  <si>
-    <t>Polônia</t>
-  </si>
-  <si>
-    <t>Elenco inicial</t>
-  </si>
-  <si>
-    <t>Wellenreuther</t>
-  </si>
-  <si>
     <t>assist_temporada</t>
   </si>
   <si>
     <t>Mais assistências numa temporada</t>
   </si>
   <si>
-    <t>Alemanha</t>
-  </si>
-  <si>
     <t>Kevin De Bruyne</t>
   </si>
   <si>
@@ -538,21 +676,12 @@
     <t>Recorde da Bundesliga na época</t>
   </si>
   <si>
-    <t>Pervan</t>
-  </si>
-  <si>
-    <t>Áustria</t>
-  </si>
-  <si>
     <t>artilheiro_historico</t>
   </si>
   <si>
     <t>Maior artilheiro da história do clube</t>
   </si>
   <si>
-    <t>Zieliński</t>
-  </si>
-  <si>
     <t>Edin Džeko</t>
   </si>
   <si>
@@ -562,156 +691,51 @@
     <t>Gols na Bundesliga</t>
   </si>
   <si>
-    <t>Vavro</t>
-  </si>
-  <si>
     <t>titulos</t>
   </si>
   <si>
-    <t>ZAG</t>
-  </si>
-  <si>
-    <t>Eslováquia</t>
-  </si>
-  <si>
     <t>Títulos de expressão</t>
   </si>
   <si>
-    <t>Wahl</t>
-  </si>
-  <si>
     <t>2009–2015</t>
   </si>
   <si>
     <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
   </si>
   <si>
-    <t>Jenz</t>
-  </si>
-  <si>
-    <t>Adjetey</t>
-  </si>
-  <si>
-    <t>Gana</t>
-  </si>
-  <si>
-    <t>Cleiton</t>
-  </si>
-  <si>
-    <t>Brasil</t>
-  </si>
-  <si>
-    <t>Angély</t>
-  </si>
-  <si>
-    <t>França</t>
-  </si>
-  <si>
-    <t>Kumbedi</t>
-  </si>
-  <si>
-    <t>LD</t>
-  </si>
-  <si>
-    <t>Fischer</t>
-  </si>
-  <si>
-    <t>Mæhle</t>
-  </si>
-  <si>
-    <t>Dinamarca</t>
-  </si>
-  <si>
-    <t>Zehnter</t>
-  </si>
-  <si>
-    <t>LE</t>
-  </si>
-  <si>
-    <t>Rogério</t>
-  </si>
-  <si>
-    <t>VOL</t>
-  </si>
-  <si>
-    <t>Grzywacz</t>
-  </si>
-  <si>
-    <t>MC</t>
-  </si>
-  <si>
-    <t>Suécia</t>
-  </si>
-  <si>
-    <t>Gerhardt</t>
-  </si>
-  <si>
-    <t>Kosovo</t>
-  </si>
-  <si>
     <t>Meta</t>
   </si>
   <si>
-    <t>Vranckx</t>
-  </si>
-  <si>
-    <t>Bélgica</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Hensel</t>
-  </si>
-  <si>
     <t>Imagem</t>
   </si>
   <si>
-    <t>Dárdai</t>
-  </si>
-  <si>
     <t>Atual</t>
   </si>
   <si>
-    <t>MEI</t>
-  </si>
-  <si>
     <t>Alvo</t>
   </si>
   <si>
-    <t>Hungria</t>
-  </si>
-  <si>
     <t>Tipo</t>
   </si>
   <si>
     <t>Subir como campeão</t>
   </si>
   <si>
-    <t>ATA</t>
-  </si>
-  <si>
     <t>Em andamento</t>
   </si>
   <si>
     <t>Conquistar o título da 2. Bundesliga e o acesso direto</t>
   </si>
   <si>
-    <t>Benedict</t>
-  </si>
-  <si>
     <t>subir-campeao.svg</t>
   </si>
   <si>
-    <t>PE</t>
-  </si>
-  <si>
     <t>Chegar às oitavas da DFB-Pokal</t>
   </si>
   <si>
-    <t>Amoura</t>
-  </si>
-  <si>
     <t>Falhou</t>
   </si>
   <si>
@@ -721,21 +745,9 @@
     <t>oitavas-pokal.svg</t>
   </si>
   <si>
-    <t>Argélia</t>
-  </si>
-  <si>
-    <t>Hornby</t>
-  </si>
-  <si>
     <t>Encontrar um novo D'Alessandro</t>
   </si>
   <si>
-    <t>Escócia</t>
-  </si>
-  <si>
-    <t>Glatzel</t>
-  </si>
-  <si>
     <t>MEI argentino, canhoto, de 15 a 23 anos</t>
   </si>
   <si>
@@ -745,21 +757,12 @@
     <t>Scouting Sul-Americano</t>
   </si>
   <si>
-    <t>Japão</t>
-  </si>
-  <si>
     <t>Ter no elenco no mínimo 5 jogadores sul-americanos</t>
   </si>
   <si>
     <t>scouting-sulamericano.svg</t>
   </si>
   <si>
-    <t>Besio</t>
-  </si>
-  <si>
-    <t>Suíça</t>
-  </si>
-  <si>
     <t>sulamericanos</t>
   </si>
   <si>
@@ -770,9 +773,6 @@
   </si>
   <si>
     <t>academia.svg</t>
-  </si>
-  <si>
-    <t>Base</t>
   </si>
   <si>
     <t>Regras de contratação por janela</t>
@@ -862,14 +862,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
-      <color rgb="FF2E7D32"/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11.0"/>
+      <color rgb="FF2E7D32"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -926,10 +926,10 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -946,7 +946,7 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
@@ -1215,83 +1215,83 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
+      <c r="A8" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -1299,32 +1299,32 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -1332,7 +1332,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -2331,14 +2331,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>136</v>
+      <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>261</v>
@@ -3383,39 +3383,39 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>263</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>258</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J1" s="12" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B2" s="6">
         <v>1.0</v>
@@ -3427,13 +3427,13 @@
         <v>265</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="F2" s="6">
         <v>34.0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>266</v>
@@ -3464,47 +3464,47 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -3512,7 +3512,7 @@
         <v>34</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>38</v>
@@ -3523,106 +3523,106 @@
         <v>41</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B11" s="5">
         <v>2.0</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B12" s="5">
         <v>3.0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B13" s="5">
         <v>16.0</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B14" s="5">
         <v>17.0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -4630,23 +4630,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>30</v>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -4654,19 +4654,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D2" s="7">
         <v>46302.0</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -4674,19 +4674,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D3" s="7">
         <v>46304.0</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4">
@@ -4694,19 +4694,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D4" s="7">
         <v>46308.0</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
@@ -4714,19 +4714,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D5" s="7">
         <v>46311.0</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6">
@@ -4734,16 +4734,16 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D6" s="7">
         <v>46315.0</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>110</v>
@@ -5764,32 +5764,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2">
@@ -5800,19 +5800,19 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E2" s="6">
         <v>1.0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H2" s="6">
         <v>4.0</v>
@@ -5829,19 +5829,19 @@
         <v>1.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E3" s="6">
         <v>1.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H3" s="6">
         <v>4.0</v>
@@ -5858,10 +5858,10 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E4" s="6">
         <v>2.0</v>
@@ -5887,10 +5887,10 @@
         <v>1.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E5" s="6">
         <v>3.0</v>
@@ -5916,19 +5916,19 @@
         <v>2.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E6" s="6">
         <v>4.0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H6" s="6">
         <v>2.0</v>
@@ -5945,16 +5945,16 @@
         <v>2.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E7" s="6">
         <v>5.0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>82</v>
@@ -5974,19 +5974,19 @@
         <v>2.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E8" s="6">
         <v>6.0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H8" s="6">
         <v>1.0</v>
@@ -6003,16 +6003,16 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E9" s="6">
         <v>7.0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>82</v>
@@ -6032,19 +6032,19 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E10" s="6">
         <v>8.0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H10" s="6">
         <v>4.0</v>
@@ -6061,16 +6061,16 @@
         <v>3.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E11" s="6">
         <v>9.0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>82</v>
@@ -6090,19 +6090,19 @@
         <v>3.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E12" s="6">
         <v>2.0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H12" s="6">
         <v>0.0</v>
@@ -6119,19 +6119,19 @@
         <v>3.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E13" s="6">
         <v>10.0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H13" s="6">
         <v>5.0</v>
@@ -6148,16 +6148,16 @@
         <v>4.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E14" s="6">
         <v>11.0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>82</v>
@@ -6177,19 +6177,19 @@
         <v>4.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E15" s="6">
         <v>12.0</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H15" s="6">
         <v>1.0</v>
@@ -6206,16 +6206,16 @@
         <v>4.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E16" s="6">
         <v>13.0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>82</v>
@@ -6235,19 +6235,19 @@
         <v>5.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E17" s="6">
         <v>14.0</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H17" s="6">
         <v>1.0</v>
@@ -6264,16 +6264,16 @@
         <v>5.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E18" s="6">
         <v>15.0</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>82</v>
@@ -6293,19 +6293,19 @@
         <v>5.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E19" s="6">
         <v>16.0</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H19" s="6">
         <v>2.0</v>
@@ -10268,16 +10268,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>113</v>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
         <v>114</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3">
@@ -10303,7 +10303,7 @@
         <v>38.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>114</v>
@@ -10317,10 +10317,10 @@
         <v>50.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5">
@@ -10331,7 +10331,7 @@
         <v>57.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>114</v>
@@ -10345,10 +10345,10 @@
         <v>17.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7">
@@ -10359,10 +10359,10 @@
         <v>42.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
@@ -10373,7 +10373,7 @@
         <v>59.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9">
@@ -10384,10 +10384,10 @@
         <v>86.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -10398,10 +10398,10 @@
         <v>28.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -10423,10 +10423,10 @@
         <v>45.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13">
@@ -10437,10 +10437,10 @@
         <v>82.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -10451,10 +10451,10 @@
         <v>8.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15">
@@ -10465,10 +10465,10 @@
         <v>80.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">
@@ -10479,10 +10479,10 @@
         <v>75.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17">
@@ -10493,7 +10493,7 @@
         <v>73.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>114</v>
@@ -10507,7 +10507,7 @@
         <v>28.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>114</v>
@@ -10521,10 +10521,10 @@
         <v>35.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
@@ -10535,7 +10535,7 @@
         <v>40.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>114</v>
@@ -10549,7 +10549,7 @@
         <v>88.0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>114</v>
@@ -10563,7 +10563,7 @@
         <v>28.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>114</v>
@@ -10577,7 +10577,7 @@
         <v>27.0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>114</v>
@@ -10591,7 +10591,7 @@
         <v>37.0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>114</v>
@@ -10605,7 +10605,7 @@
         <v>39.0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>114</v>
@@ -10619,10 +10619,10 @@
         <v>56.0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -10647,10 +10647,10 @@
         <v>4.0</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -10664,7 +10664,7 @@
         <v>114</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -10675,7 +10675,7 @@
         <v>39.0</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>114</v>
@@ -10692,7 +10692,7 @@
         <v>114</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -10703,10 +10703,10 @@
         <v>82.0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -10717,7 +10717,7 @@
         <v>47.0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>114</v>
@@ -10731,7 +10731,7 @@
         <v>3.0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>132</v>
@@ -10745,10 +10745,10 @@
         <v>63.0</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
@@ -10759,7 +10759,7 @@
         <v>74.0</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>131</v>
@@ -10773,7 +10773,7 @@
         <v>82.0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>131</v>
@@ -11765,32 +11765,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="C1" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>125</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="2">
@@ -11830,7 +11830,7 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D3" s="6">
         <v>16.0</v>
@@ -11859,7 +11859,7 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D4" s="6">
         <v>16.0</v>
@@ -11888,7 +11888,7 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D5" s="6">
         <v>16.0</v>
@@ -11917,7 +11917,7 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D6" s="6">
         <v>16.0</v>
@@ -11946,7 +11946,7 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D7" s="6">
         <v>16.0</v>
@@ -12973,249 +12973,249 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>199</v>
+        <v>166</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
@@ -13223,111 +13223,111 @@
         <v>132</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>201</v>
+        <v>168</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>204</v>
+        <v>171</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -13335,125 +13335,125 @@
         <v>114</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>203</v>
+        <v>170</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>233</v>
+        <v>185</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>234</v>
+        <v>186</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>241</v>
+        <v>188</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>242</v>
+        <v>189</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -13461,13 +13461,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="F35" s="6">
         <v>3.0</v>
@@ -14800,30 +14800,30 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>138</v>
+        <v>196</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="C2" s="6">
         <v>10.0</v>
@@ -14832,113 +14832,113 @@
         <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>148</v>
+        <v>202</v>
       </c>
       <c r="C3" s="6">
         <v>9.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="C4" s="6">
         <v>28.0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>157</v>
+        <v>208</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>158</v>
+        <v>209</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>163</v>
+        <v>210</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="C5" s="6">
         <v>20.0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>166</v>
+        <v>212</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>167</v>
+        <v>213</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>168</v>
+        <v>214</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="C6" s="6">
         <v>66.0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>176</v>
+        <v>219</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="C7" s="6">
         <v>3.0</v>
@@ -14947,13 +14947,13 @@
         <v>22</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>145</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
@@ -16156,36 +16156,41 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="48.0"/>
-    <col customWidth="1" min="2" max="2" width="16.0"/>
-    <col customWidth="1" min="3" max="3" width="70.0"/>
-    <col customWidth="1" min="4" max="26" width="8.63"/>
+    <col customWidth="1" min="1" max="1" width="25.63"/>
+    <col customWidth="1" min="2" max="2" width="14.75"/>
+    <col customWidth="1" min="3" max="3" width="173.75"/>
+    <col customWidth="1" min="4" max="4" width="20.75"/>
+    <col customWidth="1" min="5" max="5" width="4.75"/>
+    <col customWidth="1" min="6" max="6" width="4.25"/>
+    <col customWidth="1" min="7" max="8" width="8.63"/>
+    <col customWidth="1" min="9" max="9" width="11.75"/>
+    <col customWidth="1" min="10" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>0</v>
@@ -16193,93 +16198,96 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>240</v>
+        <v>243</v>
+      </c>
+      <c r="E5" s="6">
+        <v>2.0</v>
       </c>
       <c r="F5" s="6">
         <v>5.0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">

--- a/dados/dados.xlsx
+++ b/dados/dados.xlsx
@@ -27,195 +27,240 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="282">
+  <si>
+    <t>Episodio</t>
+  </si>
+  <si>
+    <t>Chave</t>
+  </si>
+  <si>
+    <t>Jogo</t>
+  </si>
+  <si>
+    <t>Temporada</t>
+  </si>
+  <si>
+    <t>Titulo</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Link YouTube</t>
+  </si>
+  <si>
+    <t>Resumo</t>
+  </si>
+  <si>
+    <t>Competicao</t>
+  </si>
+  <si>
+    <t>Rodada</t>
+  </si>
+  <si>
+    <t>Adversario</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Gols Pro</t>
+  </si>
+  <si>
+    <t>Gols Contra</t>
+  </si>
+  <si>
+    <t>26/27</t>
+  </si>
+  <si>
+    <t>DFB-Pokal</t>
+  </si>
+  <si>
+    <t>1. FC Kaiserslautern</t>
+  </si>
+  <si>
+    <t>Casa</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Descricao</t>
+  </si>
+  <si>
+    <t>nome_portal</t>
+  </si>
+  <si>
+    <t>Histórias em Campo</t>
+  </si>
+  <si>
+    <t>Nome exibido no topo do site</t>
+  </si>
   <si>
     <t>Histórias em Campo — planilha do portal</t>
   </si>
   <si>
-    <t>Chave</t>
-  </si>
-  <si>
-    <t>Episodio</t>
-  </si>
-  <si>
-    <t>Jogo</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Descricao</t>
-  </si>
-  <si>
-    <t>nome_portal</t>
-  </si>
-  <si>
-    <t>Temporada</t>
-  </si>
-  <si>
-    <t>Competicao</t>
-  </si>
-  <si>
-    <t>Histórias em Campo</t>
-  </si>
-  <si>
-    <t>Rodada</t>
-  </si>
-  <si>
-    <t>Nome exibido no topo do site</t>
-  </si>
-  <si>
-    <t>Adversario</t>
-  </si>
-  <si>
-    <t>Local</t>
+    <t>2. Bundesliga</t>
   </si>
   <si>
     <t>clube</t>
   </si>
   <si>
+    <t>VfL Wolfsburg</t>
+  </si>
+  <si>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
+  </si>
+  <si>
+    <t>canal</t>
+  </si>
+  <si>
+    <t>@gabbiDOMFC</t>
+  </si>
+  <si>
+    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
+  </si>
+  <si>
+    <t>Nome do canal</t>
+  </si>
+  <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>link_canal</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@gabbiDOMFC</t>
+  </si>
+  <si>
+    <t>Fora</t>
+  </si>
+  <si>
+    <t>Link do canal no YouTube</t>
+  </si>
+  <si>
+    <t>temporada_atual</t>
+  </si>
+  <si>
+    <t>Temporada mostrada na página inicial</t>
+  </si>
+  <si>
+    <t>competicao_liga</t>
+  </si>
+  <si>
     <t>COMO USAR</t>
   </si>
   <si>
-    <t>Gols Pro</t>
-  </si>
-  <si>
-    <t>VfL Wolfsburg</t>
-  </si>
-  <si>
-    <t>Titulo</t>
-  </si>
-  <si>
-    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
-  </si>
-  <si>
-    <t>Gols Contra</t>
-  </si>
-  <si>
-    <t>canal</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>@gabbiDOMFC</t>
-  </si>
-  <si>
-    <t>Nome do canal</t>
-  </si>
-  <si>
-    <t>Link YouTube</t>
-  </si>
-  <si>
-    <t>Resumo</t>
-  </si>
-  <si>
-    <t>link_canal</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/@gabbiDOMFC</t>
-  </si>
-  <si>
-    <t>Link do canal no YouTube</t>
-  </si>
-  <si>
-    <t>temporada_atual</t>
+    <t>Nome da liga, igual ao usado na aba Jogos</t>
+  </si>
+  <si>
+    <t>Karlsruher SC</t>
+  </si>
+  <si>
+    <t>cor_primaria</t>
+  </si>
+  <si>
+    <t>#65B32E</t>
+  </si>
+  <si>
+    <t>Cor principal do site (código hexadecimal)</t>
+  </si>
+  <si>
+    <t>cor_secundaria</t>
+  </si>
+  <si>
+    <t>#1E4D2B</t>
+  </si>
+  <si>
+    <t>Cor de apoio (fundo do topo)</t>
+  </si>
+  <si>
+    <t>escudo</t>
+  </si>
+  <si>
+    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
   </si>
   <si>
     <t>1. Cada aba alimenta uma parte do site. Não renomeie as abas nem os títulos das colunas (linha 1).</t>
   </si>
   <si>
-    <t>2026/27</t>
-  </si>
-  <si>
-    <t>Temporada mostrada na página inicial</t>
+    <t>zona_acesso</t>
+  </si>
+  <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Até esta posição: acesso direto</t>
   </si>
   <si>
     <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
   </si>
   <si>
-    <t>competicao_liga</t>
-  </si>
-  <si>
-    <t>2. Bundesliga</t>
-  </si>
-  <si>
-    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
+    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
+  </si>
+  <si>
+    <t>zona_playoff_acesso</t>
   </si>
   <si>
     <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
   </si>
   <si>
-    <t>Nome da liga, igual ao usado na aba Jogos</t>
-  </si>
-  <si>
-    <t>cor_primaria</t>
-  </si>
-  <si>
-    <t>#65B32E</t>
+    <t>Posição do playoff de acesso</t>
+  </si>
+  <si>
+    <t>zona_playoff_rebaixamento</t>
+  </si>
+  <si>
+    <t>Posição do playoff de rebaixamento</t>
   </si>
   <si>
     <t>ABAS</t>
   </si>
   <si>
-    <t>Cor principal do site (código hexadecimal)</t>
-  </si>
-  <si>
-    <t>cor_secundaria</t>
+    <t>zona_rebaixamento</t>
   </si>
   <si>
     <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
   </si>
   <si>
-    <t>#1E4D2B</t>
-  </si>
-  <si>
-    <t>Cor de apoio (fundo do topo)</t>
-  </si>
-  <si>
-    <t>escudo</t>
+    <t>A partir desta posição: rebaixamento direto</t>
+  </si>
+  <si>
+    <t>dados_exemplo</t>
+  </si>
+  <si>
+    <t>FC St. Pauli</t>
+  </si>
+  <si>
+    <t>NAO</t>
+  </si>
+  <si>
+    <t>SIM mostra um aviso de dados de exemplo no site</t>
   </si>
   <si>
     <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
   </si>
   <si>
-    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
-  </si>
-  <si>
-    <t>26/27</t>
-  </si>
-  <si>
-    <t>zona_acesso</t>
-  </si>
-  <si>
     <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
   </si>
   <si>
+    <t>SV Darmstadt 98</t>
+  </si>
+  <si>
     <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
   </si>
   <si>
-    <t>Até esta posição: acesso direto</t>
-  </si>
-  <si>
-    <t>zona_playoff_acesso</t>
-  </si>
-  <si>
     <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
   </si>
   <si>
-    <t>Posição do playoff de acesso</t>
-  </si>
-  <si>
-    <t>zona_playoff_rebaixamento</t>
-  </si>
-  <si>
     <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
   </si>
   <si>
-    <t>Posição do playoff de rebaixamento</t>
-  </si>
-  <si>
-    <t>zona_rebaixamento</t>
+    <t>1. FC Nürnberg</t>
   </si>
   <si>
     <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
@@ -224,22 +269,13 @@
     <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
   </si>
   <si>
-    <t>DFB-Pokal</t>
-  </si>
-  <si>
     <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
   </si>
   <si>
-    <t>1. FC Kaiserslautern</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
-  </si>
-  <si>
     <t>EXEMPLOS DE PREENCHIMENTO</t>
   </si>
   <si>
-    <t>Casa</t>
+    <t>Heidenheim 1846</t>
   </si>
   <si>
     <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
@@ -257,68 +293,25 @@
     <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
   </si>
   <si>
+    <t>VfL Bochum</t>
+  </si>
+  <si>
     <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
   </si>
   <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Fora</t>
-  </si>
-  <si>
-    <t>A partir desta posição: rebaixamento direto</t>
-  </si>
-  <si>
-    <t>dados_exemplo</t>
-  </si>
-  <si>
-    <t>NAO</t>
-  </si>
-  <si>
-    <t>Karlsruher SC</t>
-  </si>
-  <si>
-    <t>SIM mostra um aviso de dados de exemplo no site</t>
-  </si>
-  <si>
-    <t>Fußball-Club Energie Cottbus</t>
-  </si>
-  <si>
-    <t>FC St. Pauli</t>
-  </si>
-  <si>
-    <t>SV Darmstadt 98</t>
-  </si>
-  <si>
-    <t>1. FC Nürnberg</t>
-  </si>
-  <si>
-    <t>1. Fußballclub Heidenheim 1846</t>
-  </si>
-  <si>
-    <t>VfL Bochum</t>
-  </si>
-  <si>
     <t>Sport-Club Freiburg</t>
   </si>
   <si>
-    <t>Verein für Leibesübungen von 1899</t>
+    <t>VfL Osnabrück</t>
+  </si>
+  <si>
+    <t>Hertha BSC</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
   </si>
   <si>
     <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
-  </si>
-  <si>
-    <t>Hertha BSC</t>
-  </si>
-  <si>
-    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kieler Sportvereinigung Holstein von 1900 e.V.
-</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
   </si>
   <si>
     <t xml:space="preserve">Eintracht Braunschweig
@@ -328,18 +321,24 @@
     <t>1. FC Magdeburg</t>
   </si>
   <si>
+    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
+  </si>
+  <si>
     <t>SpVgg Greuther Fürth</t>
   </si>
   <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
     <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
   </si>
   <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
     <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
   </si>
   <si>
@@ -397,6 +396,12 @@
     <t>Reese</t>
   </si>
   <si>
+    <t>Bernhardsson</t>
+  </si>
+  <si>
+    <t>Svanberg</t>
+  </si>
+  <si>
     <t>Posicao</t>
   </si>
   <si>
@@ -409,9 +414,6 @@
     <t>V</t>
   </si>
   <si>
-    <t>Bernhardsson</t>
-  </si>
-  <si>
     <t>E</t>
   </si>
   <si>
@@ -424,12 +426,6 @@
     <t>GC</t>
   </si>
   <si>
-    <t>Svanberg</t>
-  </si>
-  <si>
-    <t>Eintracht Braunschweig</t>
-  </si>
-  <si>
     <t>Rexhbeçaj</t>
   </si>
   <si>
@@ -502,21 +498,138 @@
     <t>Eslováquia</t>
   </si>
   <si>
+    <t>Wahl</t>
+  </si>
+  <si>
+    <t>Jenz</t>
+  </si>
+  <si>
+    <t>Adjetey</t>
+  </si>
+  <si>
+    <t>Gana</t>
+  </si>
+  <si>
+    <t>Cleiton</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>Angély</t>
+  </si>
+  <si>
+    <t>França</t>
+  </si>
+  <si>
+    <t>Kumbedi</t>
+  </si>
+  <si>
+    <t>LD</t>
+  </si>
+  <si>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>Mæhle</t>
+  </si>
+  <si>
+    <t>Dinamarca</t>
+  </si>
+  <si>
+    <t>Zehnter</t>
+  </si>
+  <si>
+    <t>LE</t>
+  </si>
+  <si>
+    <t>Rogério</t>
+  </si>
+  <si>
+    <t>VOL</t>
+  </si>
+  <si>
+    <t>Grzywacz</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Suécia</t>
+  </si>
+  <si>
+    <t>Gerhardt</t>
+  </si>
+  <si>
+    <t>Kosovo</t>
+  </si>
+  <si>
+    <t>Vranckx</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
+  </si>
+  <si>
+    <t>Hensel</t>
+  </si>
+  <si>
+    <t>Dárdai</t>
+  </si>
+  <si>
+    <t>MEI</t>
+  </si>
+  <si>
+    <t>Hungria</t>
+  </si>
+  <si>
+    <t>ATA</t>
+  </si>
+  <si>
+    <t>Benedict</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>Amoura</t>
+  </si>
+  <si>
+    <t>Argélia</t>
+  </si>
+  <si>
+    <t>Hornby</t>
+  </si>
+  <si>
+    <t>Escócia</t>
+  </si>
+  <si>
+    <t>Glatzel</t>
+  </si>
+  <si>
+    <t>Japão</t>
+  </si>
+  <si>
+    <t>Besio</t>
+  </si>
+  <si>
+    <t>Suíça</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Emiliano Martínez</t>
+  </si>
+  <si>
     <t>Recorde</t>
   </si>
   <si>
-    <t>Wahl</t>
-  </si>
-  <si>
     <t>Detentor</t>
   </si>
   <si>
     <t>Quando</t>
   </si>
   <si>
-    <t>Jenz</t>
-  </si>
-  <si>
     <t>Observacao</t>
   </si>
   <si>
@@ -526,63 +639,36 @@
     <t>seq_vitorias</t>
   </si>
   <si>
-    <t>Adjetey</t>
-  </si>
-  <si>
     <t>Maior sequência de vitórias</t>
   </si>
   <si>
-    <t>Gana</t>
-  </si>
-  <si>
     <t>Bundesliga 2008/09</t>
   </si>
   <si>
     <t>Sequência da campanha do título alemão</t>
   </si>
   <si>
-    <t>Cleiton</t>
-  </si>
-  <si>
-    <t>Brasil</t>
-  </si>
-  <si>
     <t>SIM</t>
   </si>
   <si>
-    <t>Angély</t>
-  </si>
-  <si>
     <t>maior_goleada</t>
   </si>
   <si>
     <t>Maior goleada (saldo de gols)</t>
   </si>
   <si>
-    <t>França</t>
-  </si>
-  <si>
     <t>9 × 0 SV Hemelingen</t>
   </si>
   <si>
     <t>16/08/2025 · DFB-Pokal, 1ª fase</t>
   </si>
   <si>
-    <t>Kumbedi</t>
-  </si>
-  <si>
     <t>Recorde do clube na competição, confirmado pelo Wolfsburg</t>
   </si>
   <si>
-    <t>LD</t>
-  </si>
-  <si>
     <t>gols_temporada</t>
   </si>
   <si>
-    <t>Fischer</t>
-  </si>
-  <si>
     <t>Mais gols de um jogador numa temporada</t>
   </si>
   <si>
@@ -592,42 +678,27 @@
     <t>Artilheiro da Bundesliga na temporada do título</t>
   </si>
   <si>
-    <t>Mæhle</t>
-  </si>
-  <si>
     <t>assist_temporada</t>
   </si>
   <si>
     <t>Mais assistências numa temporada</t>
   </si>
   <si>
-    <t>Dinamarca</t>
-  </si>
-  <si>
     <t>Kevin De Bruyne</t>
   </si>
   <si>
     <t>Bundesliga 2014/15</t>
   </si>
   <si>
-    <t>Zehnter</t>
-  </si>
-  <si>
     <t>Recorde da Bundesliga na época</t>
   </si>
   <si>
-    <t>LE</t>
-  </si>
-  <si>
     <t>artilheiro_historico</t>
   </si>
   <si>
     <t>Maior artilheiro da história do clube</t>
   </si>
   <si>
-    <t>Rogério</t>
-  </si>
-  <si>
     <t>Edin Džeko</t>
   </si>
   <si>
@@ -643,87 +714,12 @@
     <t>Títulos de expressão</t>
   </si>
   <si>
-    <t>VOL</t>
-  </si>
-  <si>
     <t>2009–2015</t>
   </si>
   <si>
     <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
   </si>
   <si>
-    <t>Grzywacz</t>
-  </si>
-  <si>
-    <t>MC</t>
-  </si>
-  <si>
-    <t>Suécia</t>
-  </si>
-  <si>
-    <t>Gerhardt</t>
-  </si>
-  <si>
-    <t>Kosovo</t>
-  </si>
-  <si>
-    <t>Vranckx</t>
-  </si>
-  <si>
-    <t>Bélgica</t>
-  </si>
-  <si>
-    <t>Hensel</t>
-  </si>
-  <si>
-    <t>Dárdai</t>
-  </si>
-  <si>
-    <t>MEI</t>
-  </si>
-  <si>
-    <t>Hungria</t>
-  </si>
-  <si>
-    <t>ATA</t>
-  </si>
-  <si>
-    <t>Benedict</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>Amoura</t>
-  </si>
-  <si>
-    <t>Argélia</t>
-  </si>
-  <si>
-    <t>Hornby</t>
-  </si>
-  <si>
-    <t>Escócia</t>
-  </si>
-  <si>
-    <t>Glatzel</t>
-  </si>
-  <si>
-    <t>Japão</t>
-  </si>
-  <si>
-    <t>Besio</t>
-  </si>
-  <si>
-    <t>Suíça</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Emiliano Martínez</t>
-  </si>
-  <si>
     <t>Meta</t>
   </si>
   <si>
@@ -853,6 +849,12 @@
     <t>https://pt.wikipedia.org/wiki/Club_Tigres_de_la_Universidad_Aut%C3%B3noma_de_Nuevo_Le%C3%B3n</t>
   </si>
   <si>
+    <t>Selangor FA</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Selangor_F.C.</t>
+  </si>
+  <si>
     <t>Saída</t>
   </si>
   <si>
@@ -865,13 +867,7 @@
     <t>Problemas cardíacos</t>
   </si>
   <si>
-    <t>Selangor FA</t>
-  </si>
-  <si>
     <t>Sem Clube</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/wiki/Selangor_F.C.</t>
   </si>
   <si>
     <t>Passes livres</t>
@@ -902,15 +898,15 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="16.0"/>
       <color rgb="FF1E4D2B"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -971,16 +967,16 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -992,7 +988,7 @@
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1263,125 +1259,125 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
+      <c r="A1" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4"/>
+      <c r="A2" s="5"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>15</v>
+      <c r="A3" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>31</v>
+      <c r="A4" s="5" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>34</v>
+      <c r="A5" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>38</v>
+      <c r="A6" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4"/>
+      <c r="A7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>42</v>
+      <c r="A8" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>45</v>
+      <c r="A9" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
-        <v>49</v>
+      <c r="A10" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>53</v>
+      <c r="A11" s="5" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>54</v>
+      <c r="A12" s="5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>57</v>
+      <c r="A13" s="5" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>60</v>
+      <c r="A14" s="5" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>63</v>
+      <c r="A15" s="5" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>64</v>
+      <c r="A16" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="s">
-        <v>66</v>
+      <c r="A17" s="5" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4"/>
+      <c r="A18" s="5"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>69</v>
+      <c r="A19" s="5" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>71</v>
+      <c r="A20" s="5" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4" t="s">
-        <v>72</v>
+      <c r="A21" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4" t="s">
-        <v>73</v>
+      <c r="A22" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4" t="s">
-        <v>74</v>
+      <c r="A23" s="5" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4" t="s">
-        <v>75</v>
+      <c r="A24" s="5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4"/>
+      <c r="A25" s="5"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4" t="s">
-        <v>76</v>
+      <c r="A26" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -2381,13 +2377,13 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3392,48 +3388,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="12" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C2" s="6" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="B3" s="8" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="B4" s="8" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>278</v>
-      </c>
       <c r="B5" s="8" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -3460,134 +3456,134 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="2">
         <v>1.0</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F2" s="6">
+      <c r="E2" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F2" s="2">
         <v>0.0</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>277</v>
+      <c r="G2" s="2" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2">
         <v>6.0</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="C3" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F3" s="2">
         <v>1.9E7</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2">
         <v>6.0</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="C4" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F4" s="2">
         <v>7000000.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2">
         <v>6.0</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="C5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="2">
         <v>0.0</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>281</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -3613,161 +3609,161 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>21</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>39</v>
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="4" t="s">
         <v>50</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B12" s="3">
         <v>3.0</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>58</v>
+      <c r="C12" s="5" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B13" s="3">
         <v>16.0</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>61</v>
+      <c r="C13" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B14" s="3">
         <v>17.0</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>79</v>
+      <c r="C14" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>83</v>
+        <v>69</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -4776,22 +4772,22 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -4799,19 +4795,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>37</v>
+        <v>27</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D2" s="7">
         <v>46302.0</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
@@ -4819,19 +4815,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>94</v>
+        <v>27</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D3" s="7">
         <v>46304.0</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4">
@@ -4839,9 +4835,9 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>103</v>
       </c>
       <c r="D4" s="7">
@@ -4859,9 +4855,9 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>106</v>
       </c>
       <c r="D5" s="7">
@@ -4879,9 +4875,9 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D6" s="7">
@@ -4895,13 +4891,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6">
+      <c r="A7" s="2">
         <v>6.0</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>112</v>
       </c>
       <c r="D7" s="11">
@@ -4910,7 +4906,7 @@
       <c r="E7" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="2" t="s">
         <v>114</v>
       </c>
     </row>
@@ -5931,639 +5927,639 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6">
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="2">
         <v>1.0</v>
       </c>
-      <c r="B2" s="6">
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2">
         <v>1.0</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="2">
         <v>1.0</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
         <v>4.0</v>
       </c>
-      <c r="I2" s="6">
+      <c r="B5" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="2">
         <v>3.0</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6">
+      <c r="F5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="2">
         <v>2.0</v>
       </c>
-      <c r="B3" s="6">
+      <c r="I5" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="2">
         <v>1.0</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="6" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="6">
+      <c r="H9" s="2">
         <v>1.0</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="I9" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="2">
         <v>4.0</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I10" s="2">
         <v>2.0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
+    <row r="11">
+      <c r="A11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="2">
         <v>3.0</v>
       </c>
-      <c r="B4" s="6">
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="2">
         <v>1.0</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="I11" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="6">
+      <c r="H14" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="I14" s="2">
         <v>2.0</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" s="6">
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="I17" s="2">
         <v>2.0</v>
       </c>
-      <c r="I4" s="6">
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="2">
         <v>1.0</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="I20" s="2">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="I21" s="2">
         <v>1.0</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" s="6">
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="B22" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="2">
         <v>2.0</v>
       </c>
-      <c r="I5" s="6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="I10" s="6">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I11" s="6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="6">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H13" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="I13" s="6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="6">
-        <v>11.0</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="I14" s="6">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H15" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I15" s="6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I16" s="6">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="6">
-        <v>14.0</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I17" s="6">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="6">
-        <v>15.0</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I18" s="6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I19" s="6">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="6">
-        <v>17.0</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H20" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="I20" s="6">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6">
-        <v>19.0</v>
-      </c>
-      <c r="B21" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" s="6">
-        <v>18.0</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I21" s="6">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6">
-        <v>19.0</v>
-      </c>
-      <c r="B22" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="6">
-        <v>19.0</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H22" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I22" s="6">
+      <c r="I22" s="2">
         <v>2.0</v>
       </c>
     </row>
@@ -10510,7 +10506,7 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>115</v>
@@ -10523,570 +10519,570 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6">
+      <c r="A2" s="2">
         <v>1.0</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="2">
         <v>33.0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6">
+      <c r="A3" s="2">
         <v>1.0</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="2">
         <v>38.0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6">
+      <c r="A4" s="2">
         <v>1.0</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="2">
         <v>50.0</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6">
+      <c r="A5" s="2">
         <v>1.0</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="2">
         <v>57.0</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6">
+      <c r="A6" s="2">
         <v>2.0</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="2">
         <v>17.0</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6">
+      <c r="A7" s="2">
         <v>2.0</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="2">
         <v>42.0</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6">
+      <c r="A8" s="2">
         <v>2.0</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="2">
         <v>59.0</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6">
+      <c r="A9" s="2">
         <v>2.0</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="2">
         <v>86.0</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>126</v>
+      <c r="D9" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6">
+      <c r="A10" s="2">
         <v>3.0</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="2">
         <v>28.0</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6">
+      <c r="A11" s="2">
         <v>3.0</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="2">
         <v>53.0</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6">
+      <c r="A12" s="2">
         <v>4.0</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="2">
         <v>45.0</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>131</v>
+      <c r="D12" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6">
+      <c r="A13" s="2">
         <v>4.0</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="2">
         <v>82.0</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>131</v>
+      <c r="D13" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6">
+      <c r="A14" s="2">
         <v>5.0</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="2">
         <v>8.0</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>131</v>
+      <c r="D14" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6">
+      <c r="A15" s="2">
         <v>5.0</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="2">
         <v>80.0</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6">
+      <c r="A16" s="2">
         <v>7.0</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="2">
         <v>75.0</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>126</v>
+      <c r="D16" s="2" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6">
+      <c r="A17" s="2">
         <v>8.0</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="2">
         <v>73.0</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6">
+      <c r="A18" s="2">
         <v>9.0</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="2">
         <v>28.0</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6">
+      <c r="A19" s="2">
         <v>9.0</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="2">
         <v>35.0</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6">
+      <c r="A20" s="2">
         <v>9.0</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="2">
         <v>40.0</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6">
+      <c r="A21" s="2">
         <v>9.0</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="2">
         <v>88.0</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6">
+      <c r="A22" s="2">
         <v>10.0</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="2">
         <v>28.0</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6">
+      <c r="A23" s="2">
         <v>12.0</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="2">
         <v>27.0</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6">
+      <c r="A24" s="2">
         <v>12.0</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="2">
         <v>37.0</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6">
+      <c r="A25" s="2">
         <v>12.0</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="2">
         <v>39.0</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6">
+      <c r="A26" s="2">
         <v>12.0</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="2">
         <v>56.0</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="B27" s="2">
+        <v>69.0</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="B27" s="6">
-        <v>69.0</v>
-      </c>
-      <c r="C27" s="6" t="s">
+      <c r="D27" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D27" s="6" t="s">
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B28" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B29" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B30" s="2">
+        <v>39.0</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="B31" s="2">
+        <v>59.0</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="B32" s="2">
+        <v>82.0</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="B33" s="2">
+        <v>47.0</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="B34" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="B28" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="C28" s="6" t="s">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="B35" s="2">
+        <v>63.0</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="B29" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="D35" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="B36" s="2">
+        <v>74.0</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="B37" s="2">
+        <v>82.0</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B38" s="2">
+        <v>83.0</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="B39" s="2">
+        <v>51.0</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="B30" s="6">
-        <v>39.0</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" s="6" t="s">
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="B40" s="2">
+        <v>71.0</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="B41" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6">
-        <v>14.0</v>
-      </c>
-      <c r="B31" s="6">
-        <v>59.0</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6">
-        <v>15.0</v>
-      </c>
-      <c r="B32" s="6">
-        <v>82.0</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="B33" s="6">
-        <v>47.0</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6">
-        <v>17.0</v>
-      </c>
-      <c r="B34" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6">
-        <v>17.0</v>
-      </c>
-      <c r="B35" s="6">
-        <v>63.0</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6">
-        <v>18.0</v>
-      </c>
-      <c r="B36" s="6">
-        <v>74.0</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6">
-        <v>18.0</v>
-      </c>
-      <c r="B37" s="6">
-        <v>82.0</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6">
-        <v>19.0</v>
-      </c>
-      <c r="B38" s="6">
-        <v>83.0</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6">
-        <v>19.0</v>
-      </c>
-      <c r="B39" s="6">
-        <v>51.0</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="6">
-        <v>19.0</v>
-      </c>
-      <c r="B40" s="6">
-        <v>71.0</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="B41" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="B42" s="6">
+      <c r="A42" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="B42" s="2">
         <v>84.0</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D42" s="6" t="s">
+      <c r="C42" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>121</v>
       </c>
     </row>
@@ -12072,205 +12068,205 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6">
+      <c r="A2" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="F2" s="2">
         <v>5.0</v>
       </c>
-      <c r="B2" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="G2" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="H2" s="2">
+        <v>37.0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>19.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B5" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="F5" s="2">
         <v>12.0</v>
       </c>
-      <c r="F2" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="H2" s="6">
-        <v>32.0</v>
-      </c>
-      <c r="I2" s="6">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6">
+      <c r="G5" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>29.0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B6" s="2">
         <v>5.0</v>
       </c>
-      <c r="B3" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="E3" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="F3" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="C6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E6" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="I6" s="2">
         <v>21.0</v>
       </c>
-      <c r="I3" s="6">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6">
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="G7" s="2">
         <v>5.0</v>
       </c>
-      <c r="B4" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D4" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="E4" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="F4" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G4" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="H4" s="6">
-        <v>18.0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="B5" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="E5" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>18.0</v>
-      </c>
-      <c r="I5" s="6">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>23.0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="B7" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>17.0</v>
+      <c r="H7" s="2">
+        <v>26.0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>25.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -13281,518 +13277,518 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="D1" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="B28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E2" s="6" t="s">
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="s">
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="E32" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B34" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F35" s="6">
+      <c r="F35" s="2">
         <v>3.0</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6" t="s">
-        <v>230</v>
+      <c r="A36" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="B36" s="3"/>
     </row>
@@ -15120,164 +15116,164 @@
         <v>1</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>159</v>
+        <v>198</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>160</v>
+        <v>199</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C2" s="6">
+      <c r="A2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="2">
         <v>10.0</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>168</v>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>172</v>
+        <v>205</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="A3" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="2">
         <v>9.0</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>178</v>
+      <c r="D3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>172</v>
+        <v>211</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="A4" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="2">
         <v>28.0</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>168</v>
+      <c r="D4" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>172</v>
+        <v>215</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C5" s="6">
+      <c r="A5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="2">
         <v>20.0</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>192</v>
+      <c r="D5" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>172</v>
+        <v>220</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="6">
+      <c r="A6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C6" s="2">
         <v>66.0</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>200</v>
+      <c r="D6" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>172</v>
+        <v>225</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="C7" s="6">
+      <c r="A7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="2">
         <v>3.0</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>205</v>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="F7" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>172</v>
-      </c>
     </row>
     <row r="8">
-      <c r="F8" s="4"/>
+      <c r="F8" s="5"/>
       <c r="G8" s="3"/>
     </row>
     <row r="9">
@@ -16489,170 +16485,170 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="I1" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="H2" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="D3" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="H3" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="H4" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="s">
+      <c r="B5" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E5" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="I5" s="6" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="s">
+      <c r="B6" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="H6" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="H7" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="H7" s="6" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="6" t="s">
+      <c r="D8" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="H8" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="s">
+      <c r="B9" s="3"/>
+      <c r="C9" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>258</v>
+      <c r="H9" s="2" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="10">
